--- a/public/templates/newbasequotation.xlsx
+++ b/public/templates/newbasequotation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\etl-quotations\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA07B47-182E-4237-B655-6ADA22CA6E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation new" sheetId="32" r:id="rId1"/>
@@ -1558,82 +1558,72 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1678,16 +1668,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1702,7 +1692,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1717,8 +1707,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1741,6 +1730,39 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1776,39 +1798,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2124,31 +2113,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N44"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.85546875" customWidth="1"/>
-    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.88671875" customWidth="1"/>
+    <col min="9" max="9" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -2157,227 +2146,227 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="32" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="47">
+      <c r="J2" s="43">
         <v>45962</v>
       </c>
       <c r="K2" s="3"/>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="49">
+      <c r="M2" s="45">
         <v>47.7</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="7">
+      <c r="D3" s="27"/>
+      <c r="E3" s="4">
         <v>1</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="32" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="23">
         <v>45962</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="48"/>
-      <c r="N3" s="8" t="s">
+      <c r="M3" s="44"/>
+      <c r="N3" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-    </row>
-    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+    </row>
+    <row r="5" spans="1:14" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85"/>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="86" t="s">
+      <c r="B5" s="90"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+    </row>
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="87" t="s">
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="89"/>
-      <c r="H6" s="90" t="s">
+      <c r="G6" s="95"/>
+      <c r="H6" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="88"/>
-      <c r="J6" s="87" t="s">
+      <c r="I6" s="94"/>
+      <c r="J6" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="87"/>
-      <c r="L6" s="90" t="s">
+      <c r="K6" s="93"/>
+      <c r="L6" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="87"/>
-      <c r="N6" s="91"/>
-    </row>
-    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+      <c r="M6" s="93"/>
+      <c r="N6" s="97"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="94" t="s">
+      <c r="C7" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="95"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="36" t="s">
+      <c r="D7" s="78"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="36" t="s">
+      <c r="K7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="36" t="s">
+      <c r="L7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="94" t="s">
+      <c r="M7" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="97"/>
-    </row>
-    <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+      <c r="N7" s="80"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="38" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="40"/>
-    </row>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="36"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="42" t="s">
+      <c r="B9" s="37"/>
+      <c r="C9" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43" t="s">
+      <c r="F9" s="39"/>
+      <c r="G9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43" t="s">
+      <c r="H9" s="39"/>
+      <c r="I9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43" t="s">
+      <c r="J9" s="39"/>
+      <c r="K9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43" t="s">
+      <c r="L9" s="39"/>
+      <c r="M9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="44" t="s">
+      <c r="N9" s="40" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="13" t="str">
+    <row r="10" spans="1:14" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="10" t="str">
         <f>IF(C10="","",C10*0.7)</f>
         <v/>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="13" t="str">
+      <c r="E10" s="10"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="10" t="str">
         <f>IF(F10=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F10,Sites!$A:$C,3,FALSE),VLOOKUP(F10,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I10" s="13" t="str">
+      <c r="I10" s="10" t="str">
         <f>IF(H10="","",IF(J2&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H10,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H10,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H10,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H10,Transfers!$E:$H,2,FALSE),
@@ -2385,32 +2374,32 @@
 VLOOKUP(H10,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J10" s="58"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="58" t="s">
+      <c r="J10" s="54"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="10">
         <f>(J3-J2)*2000</f>
         <v>0</v>
       </c>
-      <c r="N10" s="14"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13" t="str">
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10" t="str">
         <f t="shared" ref="D11:D16" si="0">IF(C11="","",C11*0.7)</f>
         <v/>
       </c>
-      <c r="E11" s="13"/>
-      <c r="G11" s="13" t="str">
+      <c r="E11" s="10"/>
+      <c r="G11" s="10" t="str">
         <f>IF(F11=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F11,Sites!$A:$C,3,FALSE),VLOOKUP(F11,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H11" s="58"/>
-      <c r="I11" s="13" t="str">
+      <c r="H11" s="54"/>
+      <c r="I11" s="10" t="str">
         <f>IF(H11="","",IF(J3&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H11,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H11,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H11,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H11,Transfers!$E:$H,2,FALSE),
@@ -2418,33 +2407,33 @@
 VLOOKUP(H11,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J11" s="58"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="55" t="s">
+      <c r="J11" s="54"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="10">
         <f>(J3-J2)*400</f>
         <v>0</v>
       </c>
-      <c r="N11" s="14"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="13" t="str">
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="13" t="str">
+      <c r="E12" s="10"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="10" t="str">
         <f>IF(F12=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F12,Sites!$A:$C,3,FALSE),VLOOKUP(F12,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="13" t="str">
+      <c r="H12" s="8"/>
+      <c r="I12" s="10" t="str">
         <f>IF(H12="","",IF(J4&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H12,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H12,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H12,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H12,Transfers!$E:$H,2,FALSE),
@@ -2452,28 +2441,28 @@
 VLOOKUP(H12,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J12" s="58"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="14"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="13" t="str">
+      <c r="J12" s="54"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="13" t="str">
+      <c r="E13" s="10"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="10" t="str">
         <f>IF(F13=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F13,Sites!$A:$C,3,FALSE),VLOOKUP(F13,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="13" t="str">
+      <c r="H13" s="8"/>
+      <c r="I13" s="10" t="str">
         <f>IF(H13="","",IF(J5&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H13,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H13,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H13,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H13,Transfers!$E:$H,2,FALSE),
@@ -2481,28 +2470,28 @@
 VLOOKUP(H13,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J13" s="58"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="14"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13" t="str">
+      <c r="J13" s="54"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="13" t="str">
+      <c r="E14" s="10"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="10" t="str">
         <f>IF(F14=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F14,Sites!$A:$C,3,FALSE),VLOOKUP(F14,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H14" s="58"/>
-      <c r="I14" s="13" t="str">
+      <c r="H14" s="54"/>
+      <c r="I14" s="10" t="str">
         <f>IF(H14="","",IF(J6&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H14,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H14,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H14,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H14,Transfers!$E:$H,2,FALSE),
@@ -2510,28 +2499,28 @@
 VLOOKUP(H14,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J14" s="58"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="14"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13" t="str">
+      <c r="J14" s="54"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="13" t="str">
+      <c r="E15" s="10"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="10" t="str">
         <f>IF(F15=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F15,Sites!$A:$C,3,FALSE),VLOOKUP(F15,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H15" s="58"/>
-      <c r="I15" s="13" t="str">
+      <c r="H15" s="54"/>
+      <c r="I15" s="10" t="str">
         <f>IF(H15="","",IF(J7&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H15,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H15,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H15,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H15,Transfers!$E:$H,2,FALSE),
@@ -2539,28 +2528,28 @@
 VLOOKUP(H15,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J15" s="58"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="14"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13" t="str">
+      <c r="J15" s="54"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="13" t="str">
+      <c r="E16" s="10"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="10" t="str">
         <f>IF(F16=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F16,Sites!$A:$C,3,FALSE),VLOOKUP(F16,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H16" s="58"/>
-      <c r="I16" s="13" t="str">
+      <c r="H16" s="54"/>
+      <c r="I16" s="10" t="str">
         <f>IF(H16="","",IF(J8&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H16,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H16,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H16,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H16,Transfers!$E:$H,2,FALSE),
@@ -2568,25 +2557,25 @@
 VLOOKUP(H16,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J16" s="58"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="14"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="13" t="str">
+      <c r="J16" s="54"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="10" t="str">
         <f>IF(F17=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F17,Sites!$A:$C,3,FALSE),VLOOKUP(F17,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="13" t="str">
+      <c r="H17" s="8"/>
+      <c r="I17" s="10" t="str">
         <f>IF(H17="","",IF(J9&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H17,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H17,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H17,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H17,Transfers!$E:$H,2,FALSE),
@@ -2594,25 +2583,25 @@
 VLOOKUP(H17,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J17" s="58"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="14"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="13" t="str">
+      <c r="J17" s="54"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="10" t="str">
         <f>IF(F18=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F18,Sites!$A:$C,3,FALSE),VLOOKUP(F18,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H18" s="58"/>
-      <c r="I18" s="13" t="str">
+      <c r="H18" s="54"/>
+      <c r="I18" s="10" t="str">
         <f>IF(H18="","",IF(J10&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H18,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H18,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H18,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H18,Transfers!$E:$H,2,FALSE),
@@ -2620,25 +2609,25 @@
 VLOOKUP(H18,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J18" s="58"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="14"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="13" t="str">
+      <c r="J18" s="54"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="10" t="str">
         <f>IF(F19=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F19,Sites!$A:$C,3,FALSE),VLOOKUP(F19,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H19" s="58"/>
-      <c r="I19" s="13" t="str">
+      <c r="H19" s="54"/>
+      <c r="I19" s="10" t="str">
         <f>IF(H19="","",IF(J11&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H19,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H19,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H19,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H19,Transfers!$E:$H,2,FALSE),
@@ -2646,25 +2635,25 @@
 VLOOKUP(H19,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J19" s="58"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="14"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="13" t="str">
+      <c r="J19" s="54"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="10" t="str">
         <f>IF(F20=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F20,Sites!$A:$C,3,FALSE),VLOOKUP(F20,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H20" s="58"/>
-      <c r="I20" s="13" t="str">
+      <c r="H20" s="54"/>
+      <c r="I20" s="10" t="str">
         <f>IF(H20="","",IF(J12&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H20,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H20,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H20,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H20,Transfers!$E:$H,2,FALSE),
@@ -2672,25 +2661,25 @@
 VLOOKUP(H20,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J20" s="58"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="14"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="13" t="str">
+      <c r="J20" s="54"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="10" t="str">
         <f>IF(F21=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F21,Sites!$A:$C,3,FALSE),VLOOKUP(F21,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="13" t="str">
+      <c r="H21" s="8"/>
+      <c r="I21" s="10" t="str">
         <f>IF(H21="","",IF(J13&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H21,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H21,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H21,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H21,Transfers!$E:$H,2,FALSE),
@@ -2698,25 +2687,25 @@
 VLOOKUP(H21,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J21" s="58"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="14"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="13" t="str">
+      <c r="J21" s="54"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="10" t="str">
         <f>IF(F22=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F22,Sites!$A:$C,3,FALSE),VLOOKUP(F22,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H22" s="58"/>
-      <c r="I22" s="13" t="str">
+      <c r="H22" s="54"/>
+      <c r="I22" s="10" t="str">
         <f>IF(H22="","",IF(J14&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H22,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H22,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H22,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H22,Transfers!$E:$H,2,FALSE),
@@ -2724,25 +2713,25 @@
 VLOOKUP(H22,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J22" s="58"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="14"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="13" t="str">
+      <c r="J22" s="54"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="10" t="str">
         <f>IF(F23=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F23,Sites!$A:$C,3,FALSE),VLOOKUP(F23,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H23" s="58"/>
-      <c r="I23" s="13" t="str">
+      <c r="H23" s="54"/>
+      <c r="I23" s="10" t="str">
         <f>IF(H23="","",IF(J15&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H23,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H23,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H23,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H23,Transfers!$E:$H,2,FALSE),
@@ -2750,25 +2739,25 @@
 VLOOKUP(H23,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J23" s="58"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="14"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="13" t="str">
+      <c r="J23" s="54"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="11"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="10" t="str">
         <f>IF(F24=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F24,Sites!$A:$C,3,FALSE),VLOOKUP(F24,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H24" s="58"/>
-      <c r="I24" s="13" t="str">
+      <c r="H24" s="54"/>
+      <c r="I24" s="10" t="str">
         <f>IF(H24="","",IF(J16&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H24,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H24,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H24,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H24,Transfers!$E:$H,2,FALSE),
@@ -2776,25 +2765,25 @@
 VLOOKUP(H24,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J24" s="58"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="14"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="13" t="str">
+      <c r="J24" s="54"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="10" t="str">
         <f>IF(F25=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F25,Sites!$A:$C,3,FALSE),VLOOKUP(F25,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="13" t="str">
+      <c r="H25" s="8"/>
+      <c r="I25" s="10" t="str">
         <f>IF(H25="","",IF(J17&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H25,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H25,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H25,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H25,Transfers!$E:$H,2,FALSE),
@@ -2802,25 +2791,25 @@
 VLOOKUP(H25,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J25" s="58"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="14"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="13" t="str">
+      <c r="J25" s="54"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="10" t="str">
         <f>IF(F26=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F26,Sites!$A:$C,3,FALSE),VLOOKUP(F26,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="13" t="str">
+      <c r="H26" s="8"/>
+      <c r="I26" s="10" t="str">
         <f>IF(H26="","",IF(J18&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H26,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H26,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H26,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H26,Transfers!$E:$H,2,FALSE),
@@ -2828,25 +2817,25 @@
 VLOOKUP(H26,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J26" s="58"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="14"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="13" t="str">
+      <c r="J26" s="54"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="10" t="str">
         <f>IF(F27=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F27,Sites!$A:$C,3,FALSE),VLOOKUP(F27,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="13" t="str">
+      <c r="H27" s="8"/>
+      <c r="I27" s="10" t="str">
         <f>IF(H27="","",IF(J19&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H27,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H27,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H27,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H27,Transfers!$E:$H,2,FALSE),
@@ -2854,25 +2843,25 @@
 VLOOKUP(H27,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J27" s="58"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="14"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="13" t="str">
+      <c r="J27" s="54"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="11"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="10" t="str">
         <f>IF(F28=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F28,Sites!$A:$C,3,FALSE),VLOOKUP(F28,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="13" t="str">
+      <c r="H28" s="8"/>
+      <c r="I28" s="10" t="str">
         <f>IF(H28="","",IF(J20&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H28,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H28,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H28,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H28,Transfers!$E:$H,2,FALSE),
@@ -2880,25 +2869,25 @@
 VLOOKUP(H28,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J28" s="58"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="14"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="13" t="str">
+      <c r="J28" s="54"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="11"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="10" t="str">
         <f>IF(F29=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F29,Sites!$A:$C,3,FALSE),VLOOKUP(F29,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H29" s="11"/>
-      <c r="I29" s="13" t="str">
+      <c r="H29" s="8"/>
+      <c r="I29" s="10" t="str">
         <f>IF(H29="","",IF(J21&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H29,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H29,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H29,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H29,Transfers!$E:$H,2,FALSE),
@@ -2906,25 +2895,25 @@
 VLOOKUP(H29,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J29" s="58"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="14"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="13" t="str">
+      <c r="J29" s="54"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="11"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="10" t="str">
         <f>IF(F30=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F30,Sites!$A:$C,3,FALSE),VLOOKUP(F30,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="13" t="str">
+      <c r="H30" s="8"/>
+      <c r="I30" s="10" t="str">
         <f>IF(H30="","",IF(J22&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H30,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H30,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H30,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H30,Transfers!$E:$H,2,FALSE),
@@ -2932,25 +2921,25 @@
 VLOOKUP(H30,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J30" s="58"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="14"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="13" t="str">
+      <c r="J30" s="54"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="11"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="10" t="str">
         <f>IF(F31=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F31,Sites!$A:$C,3,FALSE),VLOOKUP(F31,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="13" t="str">
+      <c r="H31" s="8"/>
+      <c r="I31" s="10" t="str">
         <f>IF(H31="","",IF(J23&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H31,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H31,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H31,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H31,Transfers!$E:$H,2,FALSE),
@@ -2958,25 +2947,25 @@
 VLOOKUP(H31,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J31" s="58"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="14"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="13" t="str">
+      <c r="J31" s="54"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="11"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="10" t="str">
         <f>IF(F32=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F32,Sites!$A:$C,3,FALSE),VLOOKUP(F32,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H32" s="11"/>
-      <c r="I32" s="13" t="str">
+      <c r="H32" s="8"/>
+      <c r="I32" s="10" t="str">
         <f>IF(H32="","",IF(J24&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H32,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H32,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H32,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H32,Transfers!$E:$H,2,FALSE),
@@ -2984,25 +2973,25 @@
 VLOOKUP(H32,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J32" s="58"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="14"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="13" t="str">
+      <c r="J32" s="54"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="10" t="str">
         <f>IF(F33=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F33,Sites!$A:$C,3,FALSE),VLOOKUP(F33,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H33" s="11"/>
-      <c r="I33" s="13" t="str">
+      <c r="H33" s="8"/>
+      <c r="I33" s="10" t="str">
         <f>IF(H33="","",IF(J25&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H33,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H33,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H33,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H33,Transfers!$E:$H,2,FALSE),
@@ -3010,25 +2999,25 @@
 VLOOKUP(H33,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J33" s="58"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="14"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="13" t="str">
+      <c r="J33" s="54"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="11"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="10" t="str">
         <f>IF(F34=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F34,Sites!$A:$C,3,FALSE),VLOOKUP(F34,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H34" s="11"/>
-      <c r="I34" s="13" t="str">
+      <c r="H34" s="8"/>
+      <c r="I34" s="10" t="str">
         <f>IF(H34="","",IF(J26&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H34,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H34,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H34,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H34,Transfers!$E:$H,2,FALSE),
@@ -3036,25 +3025,25 @@
 VLOOKUP(H34,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J34" s="58"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="14"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="13" t="str">
+      <c r="J34" s="54"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="11"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="10" t="str">
         <f>IF(F35=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F35,Sites!$A:$C,3,FALSE),VLOOKUP(F35,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H35" s="11"/>
-      <c r="I35" s="13" t="str">
+      <c r="H35" s="8"/>
+      <c r="I35" s="10" t="str">
         <f>IF(H35="","",IF(J27&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H35,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H35,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H35,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H35,Transfers!$E:$H,2,FALSE),
@@ -3062,25 +3051,25 @@
 VLOOKUP(H35,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J35" s="58"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="14"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="13" t="str">
+      <c r="J35" s="54"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="10" t="str">
         <f>IF(F36=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F36,Sites!$A:$C,3,FALSE),VLOOKUP(F36,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="13" t="str">
+      <c r="H36" s="8"/>
+      <c r="I36" s="10" t="str">
         <f>IF(H36="","",IF(J28&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H36,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H36,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H36,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H36,Transfers!$E:$H,2,FALSE),
@@ -3088,25 +3077,25 @@
 VLOOKUP(H36,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J36" s="58"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="58"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="14"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="13" t="str">
+      <c r="J36" s="54"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="11"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="10" t="str">
         <f>IF(F37=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F37,Sites!$A:$C,3,FALSE),VLOOKUP(F37,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H37" s="11"/>
-      <c r="I37" s="13" t="str">
+      <c r="H37" s="8"/>
+      <c r="I37" s="10" t="str">
         <f>IF(H37="","",IF(J29&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H37,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H37,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H37,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H37,Transfers!$E:$H,2,FALSE),
@@ -3114,25 +3103,25 @@
 VLOOKUP(H37,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J37" s="58"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="58"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="14"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="60"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="13" t="str">
+      <c r="J37" s="54"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="11"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="10" t="str">
         <f>IF(F38=""," ",IF(J$2&gt;=DATE(2025,11,1),VLOOKUP(F38,Sites!$A:$C,3,FALSE),VLOOKUP(F38,Sites!$A:$B,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H38" s="11"/>
-      <c r="I38" s="13" t="str">
+      <c r="H38" s="8"/>
+      <c r="I38" s="10" t="str">
         <f>IF(H38="","",IF(J30&lt;DATE(2025,11,1),IF(E$3&lt;=7,VLOOKUP(H38,Transfers!$A:$D,2,FALSE),
 IF(E$3&lt;=15,VLOOKUP(H38,Transfers!$A:$D,3,FALSE),
 VLOOKUP(H38,Transfers!$A:$D,4,FALSE))),IF(E$3&lt;=7,VLOOKUP(H38,Transfers!$E:$H,2,FALSE),
@@ -3140,53 +3129,53 @@
 VLOOKUP(H38,Transfers!$E:$H,4,FALSE)))))</f>
         <v/>
       </c>
-      <c r="J38" s="58"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="14"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J38" s="54"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="11"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="62">
+      <c r="B39" s="47"/>
+      <c r="C39" s="58">
         <f>IF((COUNTA(B10:B36)=0),0,SUM(C10:C38))</f>
         <v>0</v>
       </c>
-      <c r="D39" s="61">
+      <c r="D39" s="57">
         <f>IF((D10)=0,"  ",SUM(D10:D38))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="61" t="str">
+      <c r="E39" s="57" t="str">
         <f>IF((E10)=0,"  ",SUM(E10:E38))</f>
         <v xml:space="preserve">  </v>
       </c>
-      <c r="F39" s="62"/>
-      <c r="G39" s="64">
+      <c r="F39" s="58"/>
+      <c r="G39" s="60">
         <f>IF((G10)=0,"  ",SUM(G10:G38)/(M2))</f>
         <v>0</v>
       </c>
-      <c r="H39" s="53"/>
-      <c r="I39" s="54">
+      <c r="H39" s="49"/>
+      <c r="I39" s="50">
         <f>IF((G10)=" ",0,SUM(I10:I38)/$M$2/$E$3)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="53"/>
-      <c r="K39" s="52">
+      <c r="J39" s="49"/>
+      <c r="K39" s="48">
         <f>IF((K10)=0,0,SUM(K10:K38)/(M2))</f>
         <v>0</v>
       </c>
-      <c r="L39" s="53"/>
-      <c r="M39" s="54">
+      <c r="L39" s="49"/>
+      <c r="M39" s="50">
         <f>IF((L10)=0,"  ",SUM(M10:M38)/$M$2/$E$3)</f>
         <v>0</v>
       </c>
-      <c r="N39" s="54">
+      <c r="N39" s="50">
         <f>IF((M10)=" ","  ",SUM(N10:N38)/$E$3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -3195,110 +3184,117 @@
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
     </row>
-    <row r="41" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
-      <c r="B41" s="98" t="s">
+      <c r="B41" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="99"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="73" t="s">
+      <c r="C41" s="82"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="68" t="s">
         <v>25</v>
       </c>
       <c r="G41" s="3"/>
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="22"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="11"/>
-      <c r="B42" s="100" t="s">
+    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="101"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="65" t="s">
+      <c r="C42" s="84"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="F42" s="71">
+      <c r="F42" s="66">
         <f>C39+G39+I39+K39+M39+N39+M3</f>
         <v>0</v>
       </c>
-      <c r="G42" s="11"/>
-      <c r="H42" s="17" t="s">
+      <c r="G42" s="8"/>
+      <c r="H42" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I42" s="102"/>
-      <c r="J42" s="102"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="11"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
-      <c r="B43" s="100" t="s">
+      <c r="I42" s="85"/>
+      <c r="J42" s="85"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="8"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="8"/>
+      <c r="B43" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="101"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="24" t="s">
+      <c r="C43" s="84"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="22">
         <f>D39</f>
         <v>0</v>
       </c>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="11"/>
-    </row>
-    <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="8"/>
+    </row>
+    <row r="44" spans="1:14" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
-      <c r="B44" s="92" t="s">
+      <c r="B44" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="93"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="24" t="s">
+      <c r="C44" s="76"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F44" s="19" t="str">
+      <c r="F44" s="16" t="str">
         <f>E39</f>
         <v xml:space="preserve">  </v>
       </c>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="7"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B4:N5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:N6"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="M7:N7"/>
@@ -3306,13 +3302,6 @@
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B4:N5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:N6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3323,15 +3312,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C121"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -3342,7 +3331,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -3354,7 +3343,7 @@
         <v>635.25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -3366,7 +3355,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -3378,7 +3367,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -3390,7 +3379,7 @@
         <v>346.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -3402,7 +3391,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -3414,7 +3403,7 @@
         <v>635.25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -3426,7 +3415,7 @@
         <v>750.75000000000011</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -3438,7 +3427,7 @@
         <v>86.625</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -3450,7 +3439,7 @@
         <v>392.70000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -3462,7 +3451,7 @@
         <v>323.40000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -3474,7 +3463,7 @@
         <v>346.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -3486,7 +3475,7 @@
         <v>115.50000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -3498,7 +3487,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -3510,7 +3499,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -3522,7 +3511,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -3534,7 +3523,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -3546,7 +3535,7 @@
         <v>808.50000000000011</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -3558,7 +3547,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -3570,7 +3559,7 @@
         <v>323.40000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -3582,7 +3571,7 @@
         <v>323.40000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -3594,7 +3583,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -3606,7 +3595,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -3618,7 +3607,7 @@
         <v>462.00000000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -3630,7 +3619,7 @@
         <v>346.5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -3642,7 +3631,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -3654,7 +3643,7 @@
         <v>323.40000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -3666,7 +3655,7 @@
         <v>392.70000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -3678,7 +3667,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -3690,7 +3679,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -3702,7 +3691,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -3714,7 +3703,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -3726,7 +3715,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -3738,7 +3727,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -3750,7 +3739,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -3762,7 +3751,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -3774,7 +3763,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -3786,7 +3775,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -3798,7 +3787,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>73</v>
       </c>
@@ -3810,7 +3799,7 @@
         <v>462.00000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -3822,7 +3811,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>75</v>
       </c>
@@ -3834,7 +3823,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>76</v>
       </c>
@@ -3846,7 +3835,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -3858,7 +3847,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>78</v>
       </c>
@@ -3870,7 +3859,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>79</v>
       </c>
@@ -3882,7 +3871,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>80</v>
       </c>
@@ -3894,7 +3883,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>81</v>
       </c>
@@ -3906,7 +3895,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>82</v>
       </c>
@@ -3918,7 +3907,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>83</v>
       </c>
@@ -3930,7 +3919,7 @@
         <v>300.3</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>84</v>
       </c>
@@ -3942,7 +3931,7 @@
         <v>346.5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -3954,7 +3943,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>86</v>
       </c>
@@ -3966,7 +3955,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>87</v>
       </c>
@@ -3978,7 +3967,7 @@
         <v>577.5</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>88</v>
       </c>
@@ -3990,7 +3979,7 @@
         <v>866.25000000000011</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>89</v>
       </c>
@@ -4002,7 +3991,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>90</v>
       </c>
@@ -4014,7 +4003,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -4026,7 +4015,7 @@
         <v>508.20000000000005</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>92</v>
       </c>
@@ -4038,7 +4027,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>93</v>
       </c>
@@ -4050,7 +4039,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>94</v>
       </c>
@@ -4062,7 +4051,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>95</v>
       </c>
@@ -4074,7 +4063,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>96</v>
       </c>
@@ -4086,7 +4075,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>97</v>
       </c>
@@ -4098,7 +4087,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>98</v>
       </c>
@@ -4110,7 +4099,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>99</v>
       </c>
@@ -4122,7 +4111,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>100</v>
       </c>
@@ -4134,7 +4123,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>101</v>
       </c>
@@ -4146,7 +4135,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>102</v>
       </c>
@@ -4158,7 +4147,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>103</v>
       </c>
@@ -4170,7 +4159,7 @@
         <v>808.50000000000011</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>104</v>
       </c>
@@ -4182,7 +4171,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>105</v>
       </c>
@@ -4194,7 +4183,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>106</v>
       </c>
@@ -4206,7 +4195,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>107</v>
       </c>
@@ -4218,7 +4207,7 @@
         <v>2887.5000000000005</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>108</v>
       </c>
@@ -4230,7 +4219,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>109</v>
       </c>
@@ -4242,7 +4231,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>110</v>
       </c>
@@ -4254,7 +4243,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>111</v>
       </c>
@@ -4266,7 +4255,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>112</v>
       </c>
@@ -4278,7 +4267,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>113</v>
       </c>
@@ -4290,7 +4279,7 @@
         <v>462.00000000000006</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>114</v>
       </c>
@@ -4302,7 +4291,7 @@
         <v>866.25000000000011</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>115</v>
       </c>
@@ -4314,7 +4303,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>116</v>
       </c>
@@ -4326,7 +4315,7 @@
         <v>635.25</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>117</v>
       </c>
@@ -4338,7 +4327,7 @@
         <v>635.25</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>118</v>
       </c>
@@ -4350,7 +4339,7 @@
         <v>519.75</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>119</v>
       </c>
@@ -4362,7 +4351,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>120</v>
       </c>
@@ -4374,7 +4363,7 @@
         <v>254.10000000000002</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>121</v>
       </c>
@@ -4386,7 +4375,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>122</v>
       </c>
@@ -4398,7 +4387,7 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>123</v>
       </c>
@@ -4410,7 +4399,7 @@
         <v>462.00000000000006</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>262</v>
       </c>
@@ -4422,7 +4411,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>263</v>
       </c>
@@ -4434,7 +4423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>249</v>
       </c>
@@ -4446,7 +4435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>250</v>
       </c>
@@ -4458,7 +4447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>252</v>
       </c>
@@ -4470,7 +4459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>261</v>
       </c>
@@ -4482,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>260</v>
       </c>
@@ -4494,7 +4483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>259</v>
       </c>
@@ -4506,7 +4495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>258</v>
       </c>
@@ -4518,7 +4507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>257</v>
       </c>
@@ -4530,7 +4519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>256</v>
       </c>
@@ -4542,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>255</v>
       </c>
@@ -4554,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>254</v>
       </c>
@@ -4566,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>253</v>
       </c>
@@ -4578,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>251</v>
       </c>
@@ -4590,7 +4579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>124</v>
       </c>
@@ -4602,8 +4591,8 @@
         <v>231.00000000000003</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A107" s="68" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="64" t="s">
         <v>125</v>
       </c>
       <c r="B107">
@@ -4614,8 +4603,8 @@
         <v>614.25</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A108" s="68" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="64" t="s">
         <v>126</v>
       </c>
       <c r="B108">
@@ -4626,8 +4615,8 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A109" s="68" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="64" t="s">
         <v>127</v>
       </c>
       <c r="B109">
@@ -4638,8 +4627,8 @@
         <v>341.25</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A110" s="68" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="64" t="s">
         <v>128</v>
       </c>
       <c r="B110">
@@ -4650,8 +4639,8 @@
         <v>204.75</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A111" s="68" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="64" t="s">
         <v>129</v>
       </c>
       <c r="B111">
@@ -4662,8 +4651,8 @@
         <v>3412.5</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A112" s="70" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="64" t="s">
         <v>130</v>
       </c>
       <c r="B112">
@@ -4674,8 +4663,8 @@
         <v>1228.5</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A113" s="70" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="64" t="s">
         <v>131</v>
       </c>
       <c r="B113">
@@ -4686,8 +4675,8 @@
         <v>682.5</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A114" s="70" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="64" t="s">
         <v>132</v>
       </c>
       <c r="B114">
@@ -4698,8 +4687,8 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A115" s="70" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="64" t="s">
         <v>133</v>
       </c>
       <c r="B115">
@@ -4710,8 +4699,8 @@
         <v>2566.2000000000003</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A116" s="70" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="64" t="s">
         <v>134</v>
       </c>
       <c r="B116">
@@ -4722,8 +4711,8 @@
         <v>1774.5</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A117" s="70" t="s">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="64" t="s">
         <v>135</v>
       </c>
       <c r="B117">
@@ -4734,8 +4723,8 @@
         <v>1501.5</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A118" s="70" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="64" t="s">
         <v>136</v>
       </c>
       <c r="B118">
@@ -4746,8 +4735,8 @@
         <v>750.75</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A119" s="70" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="64" t="s">
         <v>137</v>
       </c>
       <c r="B119">
@@ -4758,8 +4747,8 @@
         <v>750.75</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A120" s="70" t="s">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="64" t="s">
         <v>138</v>
       </c>
       <c r="B120">
@@ -4770,8 +4759,8 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A121" s="70" t="s">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="64" t="s">
         <v>247</v>
       </c>
       <c r="B121">
@@ -4792,20 +4781,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AC109"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="94.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="94.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="94.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="94.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>244</v>
       </c>
@@ -4818,7 +4807,7 @@
       <c r="D1" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="E1" s="69" t="s">
         <v>246</v>
       </c>
       <c r="F1" t="s">
@@ -4830,21 +4819,21 @@
       <c r="H1" t="s">
         <v>141</v>
       </c>
-      <c r="I1" s="74">
+      <c r="I1" s="69">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="79">
+      <c r="B2" s="74">
         <v>1461.075</v>
       </c>
-      <c r="C2" s="79">
+      <c r="C2" s="74">
         <v>2295.9750000000004</v>
       </c>
-      <c r="D2" s="79">
+      <c r="D2" s="74">
         <v>4591.9500000000007</v>
       </c>
       <c r="E2" t="s">
@@ -4863,17 +4852,17 @@
         <v>5051.1450000000013</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="74">
         <v>1669.8</v>
       </c>
-      <c r="C3" s="79">
+      <c r="C3" s="74">
         <v>2643.8500000000004</v>
       </c>
-      <c r="D3" s="79">
+      <c r="D3" s="74">
         <v>5357.2750000000005</v>
       </c>
       <c r="E3" t="s">
@@ -4892,17 +4881,17 @@
         <v>5893.0025000000014</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="79">
+      <c r="B4" s="74">
         <v>1913.3125000000005</v>
       </c>
-      <c r="C4" s="79">
+      <c r="C4" s="74">
         <v>3061.3</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="74">
         <v>6122.6</v>
       </c>
       <c r="E4" t="s">
@@ -4921,17 +4910,17 @@
         <v>6734.8600000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="79">
+      <c r="B5" s="74">
         <v>3965.775000000001</v>
       </c>
-      <c r="C5" s="79">
+      <c r="C5" s="74">
         <v>7653.2500000000018</v>
       </c>
-      <c r="D5" s="79">
+      <c r="D5" s="74">
         <v>13775.849999999999</v>
       </c>
       <c r="E5" t="s">
@@ -4950,17 +4939,17 @@
         <v>15153.434999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="79">
+      <c r="B6" s="74">
         <v>2643.8500000000004</v>
       </c>
-      <c r="C6" s="79">
+      <c r="C6" s="74">
         <v>3339.6</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="74">
         <v>6540.0499999999993</v>
       </c>
       <c r="E6" t="s">
@@ -4978,19 +4967,19 @@
         <f t="shared" si="0"/>
         <v>7194.0549999999994</v>
       </c>
-      <c r="AC6" s="74"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC6" s="69"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="79">
+      <c r="B7" s="74">
         <v>5218.125</v>
       </c>
-      <c r="C7" s="79">
+      <c r="C7" s="74">
         <v>9462.2000000000007</v>
       </c>
-      <c r="D7" s="79">
+      <c r="D7" s="74">
         <v>14193.3</v>
       </c>
       <c r="E7" t="s">
@@ -5009,17 +4998,17 @@
         <v>15612.630000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="79">
+      <c r="B8" s="74">
         <v>1669.8</v>
       </c>
-      <c r="C8" s="79">
+      <c r="C8" s="74">
         <v>3061.3</v>
       </c>
-      <c r="D8" s="79">
+      <c r="D8" s="74">
         <v>5566</v>
       </c>
       <c r="E8" t="s">
@@ -5038,17 +5027,17 @@
         <v>6122.6</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="79">
+      <c r="B9" s="74">
         <v>2156.8250000000003</v>
       </c>
-      <c r="C9" s="79">
+      <c r="C9" s="74">
         <v>3826.6250000000009</v>
       </c>
-      <c r="D9" s="79">
+      <c r="D9" s="74">
         <v>8001.1250000000018</v>
       </c>
       <c r="E9" t="s">
@@ -5067,17 +5056,17 @@
         <v>8801.2375000000029</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="79">
+      <c r="B10" s="74">
         <v>2365.5500000000002</v>
       </c>
-      <c r="C10" s="79">
+      <c r="C10" s="74">
         <v>4313.6500000000005</v>
       </c>
-      <c r="D10" s="79">
+      <c r="D10" s="74">
         <v>8696.875</v>
       </c>
       <c r="E10" t="s">
@@ -5096,17 +5085,17 @@
         <v>9566.5625</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>151</v>
       </c>
-      <c r="B11" s="79">
+      <c r="B11" s="74">
         <v>3478.75</v>
       </c>
-      <c r="C11" s="79">
+      <c r="C11" s="74">
         <v>6261.7500000000009</v>
       </c>
-      <c r="D11" s="79">
+      <c r="D11" s="74">
         <v>12940.95</v>
       </c>
       <c r="E11" t="s">
@@ -5125,17 +5114,17 @@
         <v>14235.045000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="79">
+      <c r="B12" s="74">
         <v>1808.9500000000005</v>
       </c>
-      <c r="C12" s="79">
+      <c r="C12" s="74">
         <v>3826.6250000000009</v>
       </c>
-      <c r="D12" s="79">
+      <c r="D12" s="74">
         <v>7653.2500000000018</v>
       </c>
       <c r="E12" t="s">
@@ -5154,17 +5143,17 @@
         <v>8418.5750000000025</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>153</v>
       </c>
-      <c r="B13" s="79">
+      <c r="B13" s="74">
         <v>4731.1000000000004</v>
       </c>
-      <c r="C13" s="79">
+      <c r="C13" s="74">
         <v>8279.4250000000011</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="74">
         <v>14193.3</v>
       </c>
       <c r="E13" t="s">
@@ -5183,17 +5172,17 @@
         <v>15612.630000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="79">
+      <c r="B14" s="74">
         <v>5218.125</v>
       </c>
-      <c r="C14" s="79">
+      <c r="C14" s="74">
         <v>9531.7750000000015</v>
       </c>
-      <c r="D14" s="79">
+      <c r="D14" s="74">
         <v>15306.500000000004</v>
       </c>
       <c r="E14" t="s">
@@ -5212,17 +5201,17 @@
         <v>16837.150000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="79">
+      <c r="B15" s="74">
         <v>4313.6500000000005</v>
       </c>
-      <c r="C15" s="79">
+      <c r="C15" s="74">
         <v>8279.4250000000011</v>
       </c>
-      <c r="D15" s="79">
+      <c r="D15" s="74">
         <v>12940.95</v>
       </c>
       <c r="E15" t="s">
@@ -5241,17 +5230,17 @@
         <v>14235.045000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="74">
         <v>10714.550000000001</v>
       </c>
-      <c r="C16" s="79">
+      <c r="C16" s="74">
         <v>19133.125</v>
       </c>
-      <c r="D16" s="79">
+      <c r="D16" s="74">
         <v>29221.500000000007</v>
       </c>
       <c r="E16" t="s">
@@ -5270,17 +5259,17 @@
         <v>32143.650000000012</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>157</v>
       </c>
-      <c r="B17" s="79">
+      <c r="B17" s="74">
         <v>9462.2000000000007</v>
       </c>
-      <c r="C17" s="79">
+      <c r="C17" s="74">
         <v>14193.3</v>
       </c>
-      <c r="D17" s="79">
+      <c r="D17" s="74">
         <v>26021.05</v>
       </c>
       <c r="E17" t="s">
@@ -5299,17 +5288,17 @@
         <v>28623.155000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>158</v>
       </c>
-      <c r="B18" s="79">
+      <c r="B18" s="74">
         <v>5566</v>
       </c>
-      <c r="C18" s="79">
+      <c r="C18" s="74">
         <v>10992.85</v>
       </c>
-      <c r="D18" s="79">
+      <c r="D18" s="74">
         <v>16698.000000000004</v>
       </c>
       <c r="E18" t="s">
@@ -5328,17 +5317,17 @@
         <v>18367.800000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="79">
+      <c r="B19" s="74">
         <v>8070.7000000000016</v>
       </c>
-      <c r="C19" s="79">
+      <c r="C19" s="74">
         <v>12940.95</v>
       </c>
-      <c r="D19" s="79">
+      <c r="D19" s="74">
         <v>23655.500000000004</v>
       </c>
       <c r="E19" t="s">
@@ -5357,17 +5346,17 @@
         <v>26021.050000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>160</v>
       </c>
-      <c r="B20" s="79">
+      <c r="B20" s="74">
         <v>4174.5000000000009</v>
       </c>
-      <c r="C20" s="79">
+      <c r="C20" s="74">
         <v>6957.5</v>
       </c>
-      <c r="D20" s="79">
+      <c r="D20" s="74">
         <v>11479.875000000002</v>
       </c>
       <c r="E20" t="s">
@@ -5386,17 +5375,17 @@
         <v>12627.862500000003</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>161</v>
       </c>
-      <c r="B21" s="79">
+      <c r="B21" s="74">
         <v>5218.125</v>
       </c>
-      <c r="C21" s="79">
+      <c r="C21" s="74">
         <v>9601.35</v>
       </c>
-      <c r="D21" s="79">
+      <c r="D21" s="74">
         <v>15306.500000000004</v>
       </c>
       <c r="E21" t="s">
@@ -5415,17 +5404,17 @@
         <v>16837.150000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>162</v>
       </c>
-      <c r="B22" s="79">
+      <c r="B22" s="74">
         <v>5218.125</v>
       </c>
-      <c r="C22" s="79">
+      <c r="C22" s="74">
         <v>9462.2000000000007</v>
       </c>
-      <c r="D22" s="79">
+      <c r="D22" s="74">
         <v>15306.500000000004</v>
       </c>
       <c r="E22" t="s">
@@ -5444,17 +5433,17 @@
         <v>16837.150000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>163</v>
       </c>
-      <c r="B23" s="79">
+      <c r="B23" s="74">
         <v>10853.7</v>
       </c>
-      <c r="C23" s="79">
+      <c r="C23" s="74">
         <v>15584.800000000003</v>
       </c>
-      <c r="D23" s="79">
+      <c r="D23" s="74">
         <v>29221.500000000007</v>
       </c>
       <c r="E23" t="s">
@@ -5473,17 +5462,17 @@
         <v>32143.650000000012</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="79">
+      <c r="B24" s="74">
         <v>8070.7000000000016</v>
       </c>
-      <c r="C24" s="79">
+      <c r="C24" s="74">
         <v>13010.525</v>
       </c>
-      <c r="D24" s="79">
+      <c r="D24" s="74">
         <v>22959.750000000004</v>
       </c>
       <c r="E24" t="s">
@@ -5502,17 +5491,17 @@
         <v>25255.725000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>165</v>
       </c>
-      <c r="B25" s="79">
+      <c r="B25" s="74">
         <v>8070.7000000000016</v>
       </c>
-      <c r="C25" s="79">
+      <c r="C25" s="74">
         <v>13010.525</v>
       </c>
-      <c r="D25" s="79">
+      <c r="D25" s="74">
         <v>22959.750000000004</v>
       </c>
       <c r="E25" t="s">
@@ -5531,17 +5520,17 @@
         <v>25255.725000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>166</v>
       </c>
-      <c r="B26" s="79">
+      <c r="B26" s="74">
         <v>5218.125</v>
       </c>
-      <c r="C26" s="79">
+      <c r="C26" s="74">
         <v>9462.2000000000007</v>
       </c>
-      <c r="D26" s="79">
+      <c r="D26" s="74">
         <v>16002.250000000004</v>
       </c>
       <c r="E26" t="s">
@@ -5560,17 +5549,17 @@
         <v>17602.475000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="79">
+      <c r="B27" s="74">
         <v>8905.6</v>
       </c>
-      <c r="C27" s="79">
+      <c r="C27" s="74">
         <v>14193.3</v>
       </c>
-      <c r="D27" s="79">
+      <c r="D27" s="74">
         <v>25047.000000000004</v>
       </c>
       <c r="E27" t="s">
@@ -5589,17 +5578,17 @@
         <v>27551.700000000008</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>168</v>
       </c>
-      <c r="B28" s="79">
+      <c r="B28" s="74">
         <v>9462.2000000000007</v>
       </c>
-      <c r="C28" s="79">
+      <c r="C28" s="74">
         <v>15306.500000000004</v>
       </c>
-      <c r="D28" s="79">
+      <c r="D28" s="74">
         <v>29221.500000000007</v>
       </c>
       <c r="E28" t="s">
@@ -5618,17 +5607,17 @@
         <v>32143.650000000012</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="79">
+      <c r="B29" s="74">
         <v>14193.3</v>
       </c>
-      <c r="C29" s="79">
+      <c r="C29" s="74">
         <v>23655.500000000004</v>
       </c>
-      <c r="D29" s="79">
+      <c r="D29" s="74">
         <v>36874.75</v>
       </c>
       <c r="E29" t="s">
@@ -5647,17 +5636,17 @@
         <v>40562.225000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>170</v>
       </c>
-      <c r="B30" s="79">
+      <c r="B30" s="74">
         <v>18924.400000000001</v>
       </c>
-      <c r="C30" s="79">
+      <c r="C30" s="74">
         <v>27830</v>
       </c>
-      <c r="D30" s="79">
+      <c r="D30" s="74">
         <v>47311.000000000007</v>
       </c>
       <c r="E30" t="s">
@@ -5676,17 +5665,17 @@
         <v>52042.100000000013</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>248</v>
       </c>
-      <c r="B31" s="79">
+      <c r="B31" s="74">
         <v>5000</v>
       </c>
-      <c r="C31" s="79">
+      <c r="C31" s="74">
         <v>9000</v>
       </c>
-      <c r="D31" s="79">
+      <c r="D31" s="74">
         <v>16000</v>
       </c>
       <c r="E31" t="s">
@@ -5705,17 +5694,17 @@
         <v>17600</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>171</v>
       </c>
-      <c r="B32" s="79">
+      <c r="B32" s="74">
         <v>2295.9750000000004</v>
       </c>
-      <c r="C32" s="79">
+      <c r="C32" s="74">
         <v>3896.2000000000007</v>
       </c>
-      <c r="D32" s="79">
+      <c r="D32" s="74">
         <v>83490</v>
       </c>
       <c r="E32" t="s">
@@ -5734,20 +5723,20 @@
         <v>91839.000000000015</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A33" s="67" t="s">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A33" s="63" t="s">
         <v>172</v>
       </c>
-      <c r="B33" s="79">
-        <v>0</v>
-      </c>
-      <c r="C33" s="79">
-        <v>0</v>
-      </c>
-      <c r="D33" s="79">
-        <v>0</v>
-      </c>
-      <c r="E33" s="67" t="s">
+      <c r="B33" s="74">
+        <v>0</v>
+      </c>
+      <c r="C33" s="74">
+        <v>0</v>
+      </c>
+      <c r="D33" s="74">
+        <v>0</v>
+      </c>
+      <c r="E33" s="63" t="s">
         <v>172</v>
       </c>
       <c r="F33">
@@ -5763,17 +5752,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>173</v>
       </c>
-      <c r="B34" s="79">
+      <c r="B34" s="74">
         <v>931.04000000000008</v>
       </c>
-      <c r="C34" s="79">
+      <c r="C34" s="74">
         <v>1520.2137499999999</v>
       </c>
-      <c r="D34" s="79">
+      <c r="D34" s="74">
         <v>3469.5787500000001</v>
       </c>
       <c r="E34" t="s">
@@ -5792,17 +5781,17 @@
         <v>4510.4523750000008</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="79">
+      <c r="B35" s="74">
         <v>981.95624999999984</v>
       </c>
-      <c r="C35" s="79">
+      <c r="C35" s="74">
         <v>1542.0350000000001</v>
       </c>
-      <c r="D35" s="79">
+      <c r="D35" s="74">
         <v>3513.2212500000001</v>
       </c>
       <c r="E35" t="s">
@@ -5821,17 +5810,17 @@
         <v>4567.1876250000005</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>175</v>
       </c>
-      <c r="B36" s="79">
+      <c r="B36" s="74">
         <v>771.01750000000004</v>
       </c>
-      <c r="C36" s="79">
+      <c r="C36" s="74">
         <v>1265.6324999999999</v>
       </c>
-      <c r="D36" s="79">
+      <c r="D36" s="74">
         <v>2836.7625000000003</v>
       </c>
       <c r="E36" t="s">
@@ -5850,17 +5839,17 @@
         <v>3687.7912500000007</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>176</v>
       </c>
-      <c r="B37" s="79">
+      <c r="B37" s="74">
         <v>2313.0524999999998</v>
       </c>
-      <c r="C37" s="79">
+      <c r="C37" s="74">
         <v>4087.8474999999994</v>
       </c>
-      <c r="D37" s="79">
+      <c r="D37" s="74">
         <v>6990.0737499999996</v>
       </c>
       <c r="E37" t="s">
@@ -5879,17 +5868,17 @@
         <v>9087.0958749999991</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>177</v>
       </c>
-      <c r="B38" s="79">
+      <c r="B38" s="74">
         <v>3404.1149999999998</v>
       </c>
-      <c r="C38" s="79">
+      <c r="C38" s="74">
         <v>5855.3687500000005</v>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="74">
         <v>10561.484999999999</v>
       </c>
       <c r="E38" t="s">
@@ -5907,19 +5896,19 @@
         <f t="shared" si="6"/>
         <v>13729.930499999999</v>
       </c>
-      <c r="AC38" s="67"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC38" s="63"/>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>178</v>
       </c>
-      <c r="B39" s="79">
+      <c r="B39" s="74">
         <v>3396.8412500000004</v>
       </c>
-      <c r="C39" s="79">
+      <c r="C39" s="74">
         <v>5768.0837499999998</v>
       </c>
-      <c r="D39" s="79">
+      <c r="D39" s="74">
         <v>10496.02125</v>
       </c>
       <c r="E39" t="s">
@@ -5938,17 +5927,17 @@
         <v>13644.827625</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>179</v>
       </c>
-      <c r="B40" s="79">
+      <c r="B40" s="74">
         <v>5135.2674999999999</v>
       </c>
-      <c r="C40" s="79">
+      <c r="C40" s="74">
         <v>8786.6899999999987</v>
       </c>
-      <c r="D40" s="79">
+      <c r="D40" s="74">
         <v>15907.691249999998</v>
       </c>
       <c r="E40" t="s">
@@ -5967,17 +5956,17 @@
         <v>20679.998624999997</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>180</v>
       </c>
-      <c r="B41" s="79">
+      <c r="B41" s="74">
         <v>4335.1549999999997</v>
       </c>
-      <c r="C41" s="79">
+      <c r="C41" s="74">
         <v>7055.5374999999995</v>
       </c>
-      <c r="D41" s="79">
+      <c r="D41" s="74">
         <v>15907.691249999998</v>
       </c>
       <c r="E41" t="s">
@@ -5996,17 +5985,17 @@
         <v>20679.998624999997</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>181</v>
       </c>
-      <c r="B42" s="79">
+      <c r="B42" s="74">
         <v>6575.47</v>
       </c>
-      <c r="C42" s="79">
+      <c r="C42" s="74">
         <v>10692.4125</v>
       </c>
-      <c r="D42" s="79">
+      <c r="D42" s="74">
         <v>18977.213749999999</v>
       </c>
       <c r="E42" t="s">
@@ -6025,17 +6014,17 @@
         <v>24670.377874999998</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>182</v>
       </c>
-      <c r="B43" s="79">
+      <c r="B43" s="74">
         <v>16256.831249999997</v>
       </c>
-      <c r="C43" s="79">
+      <c r="C43" s="74">
         <v>20766.556250000001</v>
       </c>
-      <c r="D43" s="79">
+      <c r="D43" s="74">
         <v>38565.422499999993</v>
       </c>
       <c r="E43" t="s">
@@ -6054,17 +6043,17 @@
         <v>50135.049249999996</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>183</v>
       </c>
-      <c r="B44" s="79">
+      <c r="B44" s="74">
         <v>2160.30375</v>
       </c>
-      <c r="C44" s="79">
+      <c r="C44" s="74">
         <v>3324.1037500000002</v>
       </c>
-      <c r="D44" s="79">
+      <c r="D44" s="74">
         <v>4473.3562499999989</v>
       </c>
       <c r="E44" t="s">
@@ -6083,17 +6072,17 @@
         <v>5815.3631249999989</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>184</v>
       </c>
-      <c r="B45" s="79">
+      <c r="B45" s="74">
         <v>2829.48875</v>
       </c>
-      <c r="C45" s="79">
+      <c r="C45" s="74">
         <v>4226.0487499999999</v>
       </c>
-      <c r="D45" s="79">
+      <c r="D45" s="74">
         <v>5462.5862499999994</v>
       </c>
       <c r="E45" t="s">
@@ -6112,17 +6101,17 @@
         <v>7101.3621249999997</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>185</v>
       </c>
-      <c r="B46" s="79">
+      <c r="B46" s="74">
         <v>2829.48875</v>
       </c>
-      <c r="C46" s="79">
+      <c r="C46" s="74">
         <v>4226.0487499999999</v>
       </c>
-      <c r="D46" s="79">
+      <c r="D46" s="74">
         <v>5462.5862499999994</v>
       </c>
       <c r="E46" t="s">
@@ -6141,17 +6130,17 @@
         <v>7101.3621249999997</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>131</v>
       </c>
-      <c r="B47" s="79">
+      <c r="B47" s="74">
         <v>5884.4637499999999</v>
       </c>
-      <c r="C47" s="79">
+      <c r="C47" s="74">
         <v>8604.8462499999987</v>
       </c>
-      <c r="D47" s="79">
+      <c r="D47" s="74">
         <v>15594.919999999998</v>
       </c>
       <c r="E47" t="s">
@@ -6170,17 +6159,17 @@
         <v>20273.395999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="79">
+      <c r="B48" s="74">
         <v>6059.0337500000005</v>
       </c>
-      <c r="C48" s="79">
+      <c r="C48" s="74">
         <v>8866.7012499999983</v>
       </c>
-      <c r="D48" s="79">
+      <c r="D48" s="74">
         <v>15834.953749999997</v>
       </c>
       <c r="E48" t="s">
@@ -6199,17 +6188,17 @@
         <v>20585.439874999996</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>187</v>
       </c>
-      <c r="B49" s="79">
+      <c r="B49" s="74">
         <v>3964.1937499999995</v>
       </c>
-      <c r="C49" s="79">
+      <c r="C49" s="74">
         <v>6029.9387500000003</v>
       </c>
-      <c r="D49" s="79">
+      <c r="D49" s="74">
         <v>13085.47625</v>
       </c>
       <c r="E49" t="s">
@@ -6228,17 +6217,17 @@
         <v>17011.119125000001</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>188</v>
       </c>
-      <c r="B50" s="79">
+      <c r="B50" s="74">
         <v>5360.7537499999999</v>
       </c>
-      <c r="C50" s="79">
+      <c r="C50" s="74">
         <v>7746.5437499999989</v>
       </c>
-      <c r="D50" s="79">
+      <c r="D50" s="74">
         <v>15500.361249999998</v>
       </c>
       <c r="E50" t="s">
@@ -6257,17 +6246,17 @@
         <v>20150.469624999998</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>189</v>
       </c>
-      <c r="B51" s="79">
+      <c r="B51" s="74">
         <v>14896.640000000001</v>
       </c>
-      <c r="C51" s="79">
+      <c r="C51" s="74">
         <v>19079.046249999999</v>
       </c>
-      <c r="D51" s="79">
+      <c r="D51" s="74">
         <v>34557.586249999993</v>
       </c>
       <c r="E51" t="s">
@@ -6286,17 +6275,17 @@
         <v>44924.862124999992</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>190</v>
       </c>
-      <c r="B52" s="79">
+      <c r="B52" s="74">
         <v>16605.971249999999</v>
       </c>
-      <c r="C52" s="79">
+      <c r="C52" s="74">
         <v>20941.126249999998</v>
       </c>
-      <c r="D52" s="79">
+      <c r="D52" s="74">
         <v>37452.538749999992</v>
       </c>
       <c r="E52" t="s">
@@ -6315,17 +6304,17 @@
         <v>48688.300374999992</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>191</v>
       </c>
-      <c r="B53" s="79">
+      <c r="B53" s="74">
         <v>17595.201249999998</v>
       </c>
-      <c r="C53" s="79">
+      <c r="C53" s="74">
         <v>21784.881250000002</v>
       </c>
-      <c r="D53" s="79">
+      <c r="D53" s="74">
         <v>39154.596249999995</v>
       </c>
       <c r="E53" t="s">
@@ -6344,17 +6333,17 @@
         <v>50900.975124999997</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>192</v>
       </c>
-      <c r="B54" s="79">
+      <c r="B54" s="74">
         <v>18053.447499999995</v>
       </c>
-      <c r="C54" s="79">
+      <c r="C54" s="74">
         <v>22475.887500000001</v>
       </c>
-      <c r="D54" s="79">
+      <c r="D54" s="74">
         <v>40507.513749999991</v>
       </c>
       <c r="E54" t="s">
@@ -6373,17 +6362,17 @@
         <v>52659.76787499999</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>193</v>
       </c>
-      <c r="B55" s="79">
+      <c r="B55" s="74">
         <v>17878.877499999999</v>
       </c>
-      <c r="C55" s="79">
+      <c r="C55" s="74">
         <v>22985.050000000003</v>
       </c>
-      <c r="D55" s="79">
+      <c r="D55" s="74">
         <v>41700.408749999995</v>
       </c>
       <c r="E55" t="s">
@@ -6402,17 +6391,17 @@
         <v>54210.531374999999</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>194</v>
       </c>
-      <c r="B56" s="79">
+      <c r="B56" s="74">
         <v>12096.24625</v>
       </c>
-      <c r="C56" s="79">
+      <c r="C56" s="74">
         <v>15318.517499999998</v>
       </c>
-      <c r="D56" s="79">
+      <c r="D56" s="74">
         <v>26898.327499999999</v>
       </c>
       <c r="E56" t="s">
@@ -6431,17 +6420,17 @@
         <v>34967.825750000004</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>195</v>
       </c>
-      <c r="B57" s="79">
+      <c r="B57" s="74">
         <v>26221.868749999998</v>
       </c>
-      <c r="C57" s="79">
+      <c r="C57" s="74">
         <v>33357.417499999996</v>
       </c>
-      <c r="D57" s="79">
+      <c r="D57" s="74">
         <v>52611.033749999995</v>
       </c>
       <c r="E57" t="s">
@@ -6460,17 +6449,17 @@
         <v>68394.343874999991</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>196</v>
       </c>
-      <c r="B58" s="79">
+      <c r="B58" s="74">
         <v>8262.98</v>
       </c>
-      <c r="C58" s="79">
+      <c r="C58" s="74">
         <v>11710.737500000001</v>
       </c>
-      <c r="D58" s="79">
+      <c r="D58" s="74">
         <v>22126.747500000001</v>
       </c>
       <c r="E58" t="s">
@@ -6489,17 +6478,17 @@
         <v>28764.771750000004</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>197</v>
       </c>
-      <c r="B59" s="79">
+      <c r="B59" s="74">
         <v>1527.4875000000002</v>
       </c>
-      <c r="C59" s="79">
+      <c r="C59" s="74">
         <v>2640.3712499999997</v>
       </c>
-      <c r="D59" s="79">
+      <c r="D59" s="74">
         <v>6088.1287499999999</v>
       </c>
       <c r="E59" t="s">
@@ -6518,17 +6507,17 @@
         <v>7914.5673749999996</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>198</v>
       </c>
-      <c r="B60" s="79">
+      <c r="B60" s="74">
         <v>771.01750000000004</v>
       </c>
-      <c r="C60" s="79">
+      <c r="C60" s="74">
         <v>1323.8225</v>
       </c>
-      <c r="D60" s="79">
+      <c r="D60" s="74">
         <v>3018.6062500000003</v>
       </c>
       <c r="E60" t="s">
@@ -6547,17 +6536,17 @@
         <v>3924.1881250000006</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>199</v>
       </c>
-      <c r="B61" s="79">
+      <c r="B61" s="74">
         <v>2298.5050000000001</v>
       </c>
-      <c r="C61" s="79">
+      <c r="C61" s="74">
         <v>3956.9199999999996</v>
       </c>
-      <c r="D61" s="79">
+      <c r="D61" s="74">
         <v>9055.8187499999985</v>
       </c>
       <c r="E61" t="s">
@@ -6576,14 +6565,14 @@
         <v>11772.564374999998</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B62" s="79">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="74">
         <v>771.01750000000004</v>
       </c>
-      <c r="C62" s="79">
+      <c r="C62" s="74">
         <v>1323.8225</v>
       </c>
-      <c r="D62" s="79">
+      <c r="D62" s="74">
         <v>3018.6062500000003</v>
       </c>
       <c r="F62">
@@ -6599,17 +6588,17 @@
         <v>3924.1881250000006</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>200</v>
       </c>
-      <c r="B63" s="79">
+      <c r="B63" s="74">
         <v>901.94500000000005</v>
       </c>
-      <c r="C63" s="79">
+      <c r="C63" s="74">
         <v>1483.845</v>
       </c>
-      <c r="D63" s="79">
+      <c r="D63" s="74">
         <v>3433.21</v>
       </c>
       <c r="E63" t="s">
@@ -6628,17 +6617,17 @@
         <v>4463.1729999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>201</v>
       </c>
-      <c r="B64" s="79">
+      <c r="B64" s="74">
         <v>960.13499999999988</v>
       </c>
-      <c r="C64" s="79">
+      <c r="C64" s="74">
         <v>1520.2137499999999</v>
       </c>
-      <c r="D64" s="79">
+      <c r="D64" s="74">
         <v>3491.3999999999996</v>
       </c>
       <c r="E64" t="s">
@@ -6657,17 +6646,17 @@
         <v>4538.82</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>202</v>
       </c>
-      <c r="B65" s="79">
+      <c r="B65" s="74">
         <v>1847.5325</v>
       </c>
-      <c r="C65" s="79">
+      <c r="C65" s="74">
         <v>2829.48875</v>
       </c>
-      <c r="D65" s="79">
+      <c r="D65" s="74">
         <v>5986.2962500000003</v>
       </c>
       <c r="E65" t="s">
@@ -6686,17 +6675,17 @@
         <v>7782.1851250000009</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>203</v>
       </c>
-      <c r="B66" s="79">
+      <c r="B66" s="74">
         <v>2727.65625</v>
       </c>
-      <c r="C66" s="79">
+      <c r="C66" s="74">
         <v>3476.8525</v>
       </c>
-      <c r="D66" s="79">
+      <c r="D66" s="74">
         <v>7499.236249999999</v>
       </c>
       <c r="E66" t="s">
@@ -6715,17 +6704,17 @@
         <v>9749.0071249999983</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>204</v>
       </c>
-      <c r="B67" s="79">
+      <c r="B67" s="74">
         <v>2727.65625</v>
       </c>
-      <c r="C67" s="79">
+      <c r="C67" s="74">
         <v>3476.8525</v>
       </c>
-      <c r="D67" s="79">
+      <c r="D67" s="74">
         <v>7499.236249999999</v>
       </c>
       <c r="E67" t="s">
@@ -6744,17 +6733,17 @@
         <v>9749.0071249999983</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>205</v>
       </c>
-      <c r="B68" s="79">
+      <c r="B68" s="74">
         <v>2160.30375</v>
       </c>
-      <c r="C68" s="79">
+      <c r="C68" s="74">
         <v>3033.1537499999999</v>
       </c>
-      <c r="D68" s="79">
+      <c r="D68" s="74">
         <v>6284.52</v>
       </c>
       <c r="E68" t="s">
@@ -6773,17 +6762,17 @@
         <v>8169.8760000000011</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>206</v>
       </c>
-      <c r="B69" s="79">
+      <c r="B69" s="74">
         <v>2305.7787499999995</v>
       </c>
-      <c r="C69" s="79">
+      <c r="C69" s="74">
         <v>3942.372499999999</v>
       </c>
-      <c r="D69" s="79">
+      <c r="D69" s="74">
         <v>9390.4112499999974</v>
       </c>
       <c r="E69" t="s">
@@ -6802,17 +6791,17 @@
         <v>12207.534624999997</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>207</v>
       </c>
-      <c r="B70" s="79">
+      <c r="B70" s="74">
         <v>1527.4875000000002</v>
       </c>
-      <c r="C70" s="79">
+      <c r="C70" s="74">
         <v>2618.5500000000002</v>
       </c>
-      <c r="D70" s="79">
+      <c r="D70" s="74">
         <v>6277.2462500000001</v>
       </c>
       <c r="E70" t="s">
@@ -6831,17 +6820,17 @@
         <v>8160.4201250000006</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>208</v>
       </c>
-      <c r="B71" s="79">
+      <c r="B71" s="74">
         <v>792.83875</v>
       </c>
-      <c r="C71" s="79">
+      <c r="C71" s="74">
         <v>1331.0962500000001</v>
       </c>
-      <c r="D71" s="79">
+      <c r="D71" s="74">
         <v>3142.26</v>
       </c>
       <c r="E71" t="s">
@@ -6860,17 +6849,17 @@
         <v>4084.9380000000006</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>209</v>
       </c>
-      <c r="B72" s="79">
+      <c r="B72" s="74">
         <v>3549.5899999999997</v>
       </c>
-      <c r="C72" s="79">
+      <c r="C72" s="74">
         <v>6189.9612499999994</v>
       </c>
-      <c r="D72" s="79">
+      <c r="D72" s="74">
         <v>11027.004999999999</v>
       </c>
       <c r="E72" t="s">
@@ -6889,17 +6878,17 @@
         <v>14335.1065</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>210</v>
       </c>
-      <c r="B73" s="79">
+      <c r="B73" s="74">
         <v>2451.2537499999994</v>
       </c>
-      <c r="C73" s="79">
+      <c r="C73" s="74">
         <v>4189.6799999999994</v>
       </c>
-      <c r="D73" s="79">
+      <c r="D73" s="74">
         <v>7346.4874999999993</v>
       </c>
       <c r="E73" t="s">
@@ -6918,17 +6907,17 @@
         <v>9550.4337500000001</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>211</v>
       </c>
-      <c r="B74" s="79">
+      <c r="B74" s="74">
         <v>1592.9512499999998</v>
       </c>
-      <c r="C74" s="79">
-        <v>0</v>
-      </c>
-      <c r="D74" s="79">
+      <c r="C74" s="74">
+        <v>0</v>
+      </c>
+      <c r="D74" s="74">
         <v>0</v>
       </c>
       <c r="E74" t="s">
@@ -6947,17 +6936,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>212</v>
       </c>
-      <c r="B75" s="79">
+      <c r="B75" s="74">
         <v>1251.0849999999998</v>
       </c>
-      <c r="C75" s="79">
-        <v>0</v>
-      </c>
-      <c r="D75" s="79">
+      <c r="C75" s="74">
+        <v>0</v>
+      </c>
+      <c r="D75" s="74">
         <v>0</v>
       </c>
       <c r="E75" t="s">
@@ -6976,17 +6965,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>213</v>
       </c>
-      <c r="B76" s="79">
+      <c r="B76" s="74">
         <v>640.08999999999992</v>
       </c>
-      <c r="C76" s="79">
-        <v>0</v>
-      </c>
-      <c r="D76" s="79">
+      <c r="C76" s="74">
+        <v>0</v>
+      </c>
+      <c r="D76" s="74">
         <v>0</v>
       </c>
       <c r="E76" t="s">
@@ -7005,17 +6994,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>214</v>
       </c>
-      <c r="B77" s="79">
+      <c r="B77" s="74">
         <v>2058.4712499999996</v>
       </c>
-      <c r="C77" s="79">
-        <v>0</v>
-      </c>
-      <c r="D77" s="79">
+      <c r="C77" s="74">
+        <v>0</v>
+      </c>
+      <c r="D77" s="74">
         <v>0</v>
       </c>
       <c r="E77" t="s">
@@ -7034,17 +7023,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>215</v>
       </c>
-      <c r="B78" s="79">
+      <c r="B78" s="74">
         <v>1432.92875</v>
       </c>
-      <c r="C78" s="79">
-        <v>0</v>
-      </c>
-      <c r="D78" s="79">
+      <c r="C78" s="74">
+        <v>0</v>
+      </c>
+      <c r="D78" s="74">
         <v>0</v>
       </c>
       <c r="E78" t="s">
@@ -7063,17 +7052,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>216</v>
       </c>
-      <c r="B79" s="79">
+      <c r="B79" s="74">
         <v>2473.0749999999998</v>
       </c>
-      <c r="C79" s="79">
-        <v>0</v>
-      </c>
-      <c r="D79" s="79">
+      <c r="C79" s="74">
+        <v>0</v>
+      </c>
+      <c r="D79" s="74">
         <v>0</v>
       </c>
       <c r="E79" t="s">
@@ -7092,17 +7081,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>217</v>
       </c>
-      <c r="B80" s="79">
+      <c r="B80" s="74">
         <v>2814.9412500000003</v>
       </c>
-      <c r="C80" s="79">
-        <v>0</v>
-      </c>
-      <c r="D80" s="79">
+      <c r="C80" s="74">
+        <v>0</v>
+      </c>
+      <c r="D80" s="74">
         <v>0</v>
       </c>
       <c r="E80" t="s">
@@ -7121,17 +7110,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>218</v>
       </c>
-      <c r="B81" s="79">
+      <c r="B81" s="74">
         <v>2138.4824999999996</v>
       </c>
-      <c r="C81" s="79">
-        <v>0</v>
-      </c>
-      <c r="D81" s="79">
+      <c r="C81" s="74">
+        <v>0</v>
+      </c>
+      <c r="D81" s="74">
         <v>0</v>
       </c>
       <c r="E81" t="s">
@@ -7150,17 +7139,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>219</v>
       </c>
-      <c r="B82" s="79">
+      <c r="B82" s="74">
         <v>3236.8187500000004</v>
       </c>
-      <c r="C82" s="79">
-        <v>0</v>
-      </c>
-      <c r="D82" s="79">
+      <c r="C82" s="74">
+        <v>0</v>
+      </c>
+      <c r="D82" s="74">
         <v>0</v>
       </c>
       <c r="E82" t="s">
@@ -7179,17 +7168,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>220</v>
       </c>
-      <c r="B83" s="79">
+      <c r="B83" s="74">
         <v>3753.2549999999997</v>
       </c>
-      <c r="C83" s="79">
-        <v>0</v>
-      </c>
-      <c r="D83" s="79">
+      <c r="C83" s="74">
+        <v>0</v>
+      </c>
+      <c r="D83" s="74">
         <v>0</v>
       </c>
       <c r="E83" t="s">
@@ -7208,17 +7197,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>221</v>
       </c>
-      <c r="B84" s="79">
+      <c r="B84" s="74">
         <v>2560.3599999999997</v>
       </c>
-      <c r="C84" s="79">
-        <v>0</v>
-      </c>
-      <c r="D84" s="79">
+      <c r="C84" s="74">
+        <v>0</v>
+      </c>
+      <c r="D84" s="74">
         <v>0</v>
       </c>
       <c r="E84" t="s">
@@ -7237,17 +7226,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>222</v>
       </c>
-      <c r="B85" s="79">
+      <c r="B85" s="74">
         <v>7040.99</v>
       </c>
-      <c r="C85" s="79">
-        <v>0</v>
-      </c>
-      <c r="D85" s="79">
+      <c r="C85" s="74">
+        <v>0</v>
+      </c>
+      <c r="D85" s="74">
         <v>0</v>
       </c>
       <c r="E85" t="s">
@@ -7266,17 +7255,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>223</v>
       </c>
-      <c r="B86" s="79">
+      <c r="B86" s="74">
         <v>5855.3687500000005</v>
       </c>
-      <c r="C86" s="79">
-        <v>0</v>
-      </c>
-      <c r="D86" s="79">
+      <c r="C86" s="74">
+        <v>0</v>
+      </c>
+      <c r="D86" s="74">
         <v>0</v>
       </c>
       <c r="E86" t="s">
@@ -7295,17 +7284,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>224</v>
       </c>
-      <c r="B87" s="79">
+      <c r="B87" s="74">
         <v>7499.236249999999</v>
       </c>
-      <c r="C87" s="79">
-        <v>0</v>
-      </c>
-      <c r="D87" s="79">
+      <c r="C87" s="74">
+        <v>0</v>
+      </c>
+      <c r="D87" s="74">
         <v>0</v>
       </c>
       <c r="E87" t="s">
@@ -7324,17 +7313,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>225</v>
       </c>
-      <c r="B88" s="79">
+      <c r="B88" s="74">
         <v>5462.5862499999994</v>
       </c>
-      <c r="C88" s="79">
-        <v>0</v>
-      </c>
-      <c r="D88" s="79">
+      <c r="C88" s="74">
+        <v>0</v>
+      </c>
+      <c r="D88" s="74">
         <v>0</v>
       </c>
       <c r="E88" t="s">
@@ -7353,17 +7342,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>226</v>
       </c>
-      <c r="B89" s="79">
+      <c r="B89" s="74">
         <v>4233.3224999999993</v>
       </c>
-      <c r="C89" s="79">
-        <v>0</v>
-      </c>
-      <c r="D89" s="79">
+      <c r="C89" s="74">
+        <v>0</v>
+      </c>
+      <c r="D89" s="74">
         <v>0</v>
       </c>
       <c r="E89" t="s">
@@ -7382,17 +7371,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>227</v>
       </c>
-      <c r="B90" s="79">
+      <c r="B90" s="74">
         <v>7055.5374999999995</v>
       </c>
-      <c r="C90" s="79">
-        <v>0</v>
-      </c>
-      <c r="D90" s="79">
+      <c r="C90" s="74">
+        <v>0</v>
+      </c>
+      <c r="D90" s="74">
         <v>0</v>
       </c>
       <c r="E90" t="s">
@@ -7411,17 +7400,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>228</v>
       </c>
-      <c r="B91" s="79">
+      <c r="B91" s="74">
         <v>3964.1937499999995</v>
       </c>
-      <c r="C91" s="79">
+      <c r="C91" s="74">
         <v>6029.9387500000003</v>
       </c>
-      <c r="D91" s="79">
+      <c r="D91" s="74">
         <v>13085.47625</v>
       </c>
       <c r="E91" t="s">
@@ -7440,17 +7429,17 @@
         <v>17011.119125000001</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>229</v>
       </c>
-      <c r="B92" s="79">
+      <c r="B92" s="74">
         <v>5360.7537499999999</v>
       </c>
-      <c r="C92" s="79">
+      <c r="C92" s="74">
         <v>8313.8962499999998</v>
       </c>
-      <c r="D92" s="79">
+      <c r="D92" s="74">
         <v>17078.764999999996</v>
       </c>
       <c r="E92" t="s">
@@ -7469,20 +7458,20 @@
         <v>22202.394499999995</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="67" t="s">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="B93" s="79">
-        <v>0</v>
-      </c>
-      <c r="C93" s="79">
-        <v>0</v>
-      </c>
-      <c r="D93" s="79">
-        <v>0</v>
-      </c>
-      <c r="E93" s="67" t="s">
+      <c r="B93" s="74">
+        <v>0</v>
+      </c>
+      <c r="C93" s="74">
+        <v>0</v>
+      </c>
+      <c r="D93" s="74">
+        <v>0</v>
+      </c>
+      <c r="E93" s="63" t="s">
         <v>230</v>
       </c>
       <c r="F93">
@@ -7498,17 +7487,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>231</v>
       </c>
-      <c r="B94" s="79">
+      <c r="B94" s="74">
         <v>442.75</v>
       </c>
-      <c r="C94" s="79">
+      <c r="C94" s="74">
         <v>790.62500000000011</v>
       </c>
-      <c r="D94" s="79">
+      <c r="D94" s="74">
         <v>1973.3999999999999</v>
       </c>
       <c r="E94" t="s">
@@ -7527,20 +7516,20 @@
         <v>2170.7400000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="66" t="s">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="62" t="s">
         <v>232</v>
       </c>
-      <c r="B95" s="79">
+      <c r="B95" s="74">
         <v>834.9</v>
       </c>
-      <c r="C95" s="79">
+      <c r="C95" s="74">
         <v>1593.9</v>
       </c>
-      <c r="D95" s="79">
+      <c r="D95" s="74">
         <v>2757.7000000000003</v>
       </c>
-      <c r="E95" s="66" t="s">
+      <c r="E95" s="62" t="s">
         <v>232</v>
       </c>
       <c r="F95">
@@ -7556,17 +7545,17 @@
         <v>3033.4700000000007</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>233</v>
       </c>
-      <c r="B96" s="79">
+      <c r="B96" s="74">
         <v>1252.3500000000001</v>
       </c>
-      <c r="C96" s="79">
+      <c r="C96" s="74">
         <v>2352.9</v>
       </c>
-      <c r="D96" s="79">
+      <c r="D96" s="74">
         <v>4705.8</v>
       </c>
       <c r="E96" t="s">
@@ -7585,20 +7574,20 @@
         <v>5176.380000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A97" s="66" t="s">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A97" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="B97" s="79">
+      <c r="B97" s="74">
         <v>834.9</v>
       </c>
-      <c r="C97" s="79">
+      <c r="C97" s="74">
         <v>1366.2</v>
       </c>
-      <c r="D97" s="79">
+      <c r="D97" s="74">
         <v>2757.7000000000003</v>
       </c>
-      <c r="E97" s="66" t="s">
+      <c r="E97" s="62" t="s">
         <v>123</v>
       </c>
       <c r="F97">
@@ -7614,17 +7603,17 @@
         <v>3033.4700000000007</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>114</v>
       </c>
-      <c r="B98" s="79">
+      <c r="B98" s="74">
         <v>5996.1</v>
       </c>
-      <c r="C98" s="79">
+      <c r="C98" s="74">
         <v>8956.1999999999989</v>
       </c>
-      <c r="D98" s="79">
+      <c r="D98" s="74">
         <v>17305.2</v>
       </c>
       <c r="E98" t="s">
@@ -7642,22 +7631,22 @@
         <f t="shared" si="9"/>
         <v>19035.72</v>
       </c>
-      <c r="AC98" s="67"/>
-    </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A99" s="66" t="s">
+      <c r="AC98" s="63"/>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A99" s="62" t="s">
         <v>234</v>
       </c>
-      <c r="B99" s="79">
+      <c r="B99" s="74">
         <v>1062.5999999999999</v>
       </c>
-      <c r="C99" s="79">
+      <c r="C99" s="74">
         <v>1973.3999999999999</v>
       </c>
-      <c r="D99" s="79">
+      <c r="D99" s="74">
         <v>3946.7999999999997</v>
       </c>
-      <c r="E99" s="66" t="s">
+      <c r="E99" s="62" t="s">
         <v>234</v>
       </c>
       <c r="F99">
@@ -7673,17 +7662,17 @@
         <v>4341.4800000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>235</v>
       </c>
-      <c r="B100" s="79">
+      <c r="B100" s="74">
         <v>2049.2999999999997</v>
       </c>
-      <c r="C100" s="79">
+      <c r="C100" s="74">
         <v>3946.7999999999997</v>
       </c>
-      <c r="D100" s="79">
+      <c r="D100" s="74">
         <v>7438.2</v>
       </c>
       <c r="E100" t="s">
@@ -7701,22 +7690,22 @@
         <f t="shared" si="9"/>
         <v>8182.02</v>
       </c>
-      <c r="AC100" s="66"/>
-    </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A101" s="67" t="s">
+      <c r="AC100" s="62"/>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A101" s="63" t="s">
         <v>236</v>
       </c>
-      <c r="B101" s="79">
-        <v>0</v>
-      </c>
-      <c r="C101" s="79">
-        <v>0</v>
-      </c>
-      <c r="D101" s="79">
-        <v>0</v>
-      </c>
-      <c r="E101" s="67" t="s">
+      <c r="B101" s="74">
+        <v>0</v>
+      </c>
+      <c r="C101" s="74">
+        <v>0</v>
+      </c>
+      <c r="D101" s="74">
+        <v>0</v>
+      </c>
+      <c r="E101" s="63" t="s">
         <v>236</v>
       </c>
       <c r="F101">
@@ -7732,17 +7721,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>237</v>
       </c>
-      <c r="B102" s="79">
+      <c r="B102" s="74">
         <v>385.82500000000005</v>
       </c>
-      <c r="C102" s="79">
+      <c r="C102" s="74">
         <v>531.29999999999995</v>
       </c>
-      <c r="D102" s="79">
+      <c r="D102" s="74">
         <v>1302.95</v>
       </c>
       <c r="E102" t="s">
@@ -7760,19 +7749,19 @@
         <f t="shared" si="9"/>
         <v>1433.2450000000001</v>
       </c>
-      <c r="AC102" s="66"/>
-    </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC102" s="62"/>
+    </row>
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>238</v>
       </c>
-      <c r="B103" s="79">
+      <c r="B103" s="74">
         <v>777.97500000000002</v>
       </c>
-      <c r="C103" s="79">
+      <c r="C103" s="74">
         <v>1302.95</v>
       </c>
-      <c r="D103" s="79">
+      <c r="D103" s="74">
         <v>3023.3500000000004</v>
       </c>
       <c r="E103" t="s">
@@ -7791,17 +7780,17 @@
         <v>3325.6850000000009</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>239</v>
       </c>
-      <c r="B104" s="79">
+      <c r="B104" s="74">
         <v>2839.9250000000002</v>
       </c>
-      <c r="C104" s="79">
+      <c r="C104" s="74">
         <v>3845.6</v>
       </c>
-      <c r="D104" s="79">
+      <c r="D104" s="74">
         <v>9512.8000000000011</v>
       </c>
       <c r="E104" t="s">
@@ -7819,19 +7808,19 @@
         <f t="shared" si="9"/>
         <v>10464.080000000002</v>
       </c>
-      <c r="AC104" s="66"/>
-    </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC104" s="62"/>
+    </row>
+    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>240</v>
       </c>
-      <c r="B105" s="79">
+      <c r="B105" s="74">
         <v>1733.05</v>
       </c>
-      <c r="C105" s="79">
+      <c r="C105" s="74">
         <v>2555.3000000000002</v>
       </c>
-      <c r="D105" s="79">
+      <c r="D105" s="74">
         <v>6584.3249999999998</v>
       </c>
       <c r="E105" t="s">
@@ -7850,17 +7839,17 @@
         <v>7242.7575000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>84</v>
       </c>
-      <c r="B106" s="79">
+      <c r="B106" s="74">
         <v>1878.5249999999999</v>
       </c>
-      <c r="C106" s="79">
+      <c r="C106" s="74">
         <v>2688.125</v>
       </c>
-      <c r="D106" s="79">
+      <c r="D106" s="74">
         <v>7058.7</v>
       </c>
       <c r="E106" t="s">
@@ -7878,19 +7867,19 @@
         <f t="shared" si="9"/>
         <v>7764.5700000000006</v>
       </c>
-      <c r="AC106" s="67"/>
-    </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC106" s="63"/>
+    </row>
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>241</v>
       </c>
-      <c r="B107" s="79">
+      <c r="B107" s="74">
         <v>3706.45</v>
       </c>
-      <c r="C107" s="79">
+      <c r="C107" s="74">
         <v>5863.2750000000005</v>
       </c>
-      <c r="D107" s="79">
+      <c r="D107" s="74">
         <v>13440.624999999998</v>
       </c>
       <c r="E107" t="s">
@@ -7909,17 +7898,17 @@
         <v>14784.6875</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>242</v>
       </c>
-      <c r="B108" s="79">
+      <c r="B108" s="74">
         <v>4566.6500000000005</v>
       </c>
-      <c r="C108" s="79">
+      <c r="C108" s="74">
         <v>7305.375</v>
       </c>
-      <c r="D108" s="79">
+      <c r="D108" s="74">
         <v>15749.25</v>
       </c>
       <c r="E108" t="s">
@@ -7938,17 +7927,17 @@
         <v>17324.175000000003</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="79">
+      <c r="B109" s="74">
         <v>575.57500000000005</v>
       </c>
-      <c r="C109" s="79">
+      <c r="C109" s="74">
         <v>1062.5999999999999</v>
       </c>
-      <c r="D109" s="79">
+      <c r="D109" s="74">
         <v>2163.15</v>
       </c>
       <c r="E109" t="s">
@@ -7976,35 +7965,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:Q46"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:P46"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="16.7109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="16" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" style="4" customWidth="1"/>
-    <col min="13" max="13" width="8.7109375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="7.5703125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="4" customWidth="1"/>
-    <col min="16" max="16" width="10.28515625" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="10.28515625" style="4"/>
+    <col min="2" max="2" width="22.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="13" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="13" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="7.5546875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="14.88671875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="10.33203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
+    <row r="1" spans="2:16" s="1" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -8014,1060 +8003,1054 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="2:17" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="30"/>
-      <c r="C2" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="32" t="s">
+    <row r="2" spans="2:16" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="B2" s="26"/>
+      <c r="C2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="47">
+      <c r="J2" s="43">
         <v>45509</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="49">
+      <c r="M2" s="45">
         <v>47.7</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" spans="2:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="30"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="2:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="26"/>
+      <c r="C3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="7">
+      <c r="D3" s="27"/>
+      <c r="E3" s="4">
         <v>1</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="32" t="s">
+      <c r="F3" s="5"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="23">
         <v>45513</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="50" t="s">
+      <c r="L3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="48"/>
-      <c r="N3" s="8" t="s">
+      <c r="M3" s="44"/>
+      <c r="N3" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B4" s="82" t="s">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-    </row>
-    <row r="5" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="84"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-    </row>
-    <row r="6" spans="2:17" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="86" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+    </row>
+    <row r="5" spans="2:16" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="90"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+    </row>
+    <row r="6" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="87" t="s">
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="89"/>
-      <c r="H6" s="90" t="s">
+      <c r="G6" s="95"/>
+      <c r="H6" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="88"/>
-      <c r="J6" s="87" t="s">
+      <c r="I6" s="94"/>
+      <c r="J6" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="87"/>
-      <c r="L6" s="90" t="s">
+      <c r="K6" s="93"/>
+      <c r="L6" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="87"/>
-      <c r="N6" s="91"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="9"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B7" s="35" t="s">
+      <c r="M6" s="93"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="94" t="s">
+      <c r="C7" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="95"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="36" t="s">
+      <c r="D7" s="78"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="36" t="s">
+      <c r="K7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="36" t="s">
+      <c r="L7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="94" t="s">
+      <c r="M7" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="97"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B8" s="37"/>
-      <c r="C8" s="38" t="s">
+      <c r="N7" s="80"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B9" s="41"/>
-      <c r="C9" s="42" t="s">
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" s="37"/>
+      <c r="C9" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43" t="s">
+      <c r="F9" s="39"/>
+      <c r="G9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43" t="s">
+      <c r="H9" s="39"/>
+      <c r="I9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43" t="s">
+      <c r="J9" s="39"/>
+      <c r="K9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43" t="s">
+      <c r="L9" s="39"/>
+      <c r="M9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="44" t="s">
+      <c r="N9" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-    </row>
-    <row r="10" spans="2:17" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B10" s="12"/>
-      <c r="D10" s="13" t="str">
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+    </row>
+    <row r="10" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B10" s="9"/>
+      <c r="D10" s="10" t="str">
         <f>IF(C10="","",C10*0.7)</f>
         <v/>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="13" t="str">
+      <c r="E10" s="10"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="10" t="str">
         <f>IF(F10=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F10,Sites!$A:$B,3,FALSE),VLOOKUP(F10,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H10" s="58"/>
-      <c r="I10" s="13" t="str">
+      <c r="H10" s="54"/>
+      <c r="I10" s="10" t="str">
         <f>IF(H10="", "", IF(E$3&lt;=7, VLOOKUP(H10, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H10, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H10, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J10" s="58"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="58" t="s">
+      <c r="J10" s="54"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="10">
         <f>(J3-J2)*1200</f>
         <v>4800</v>
       </c>
-      <c r="N10" s="14"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-    </row>
-    <row r="11" spans="2:17" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13" t="str">
+      <c r="N10" s="11"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10" t="str">
         <f t="shared" ref="D11:D16" si="0">IF(C11="","",C11*0.7)</f>
         <v/>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="13" t="str">
+      <c r="E11" s="10"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="10" t="str">
         <f>IF(F11=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F11,Sites!$A:$B,3,FALSE),VLOOKUP(F11,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H11" s="58"/>
-      <c r="I11" s="13" t="str">
+      <c r="H11" s="54"/>
+      <c r="I11" s="10" t="str">
         <f>IF(H11="", "", IF(E$3&lt;=7, VLOOKUP(H11, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H11, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H11, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J11" s="58"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="55" t="s">
+      <c r="J11" s="54"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="10">
         <f>(J3-J2)*200</f>
         <v>800</v>
       </c>
-      <c r="N11" s="14"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-    </row>
-    <row r="12" spans="2:17" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D12" s="13" t="str">
+      <c r="N11" s="11"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+    </row>
+    <row r="12" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="D12" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="13" t="str">
+      <c r="E12" s="10"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="10" t="str">
         <f>IF(F12=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F12,Sites!$A:$B,3,FALSE),VLOOKUP(F12,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I12" s="13" t="str">
+      <c r="I12" s="10" t="str">
         <f>IF(H12="", "", IF(E$3&lt;=7, VLOOKUP(H12, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H12, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H12, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J12" s="58"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-    </row>
-    <row r="13" spans="2:17" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D13" s="13" t="str">
+      <c r="J12" s="54"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="D13" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="13" t="str">
+      <c r="E13" s="10"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="10" t="str">
         <f>IF(F13=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F13,Sites!$A:$B,3,FALSE),VLOOKUP(F13,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I13" s="13" t="str">
+      <c r="I13" s="10" t="str">
         <f>IF(H13="", "", IF(E$3&lt;=7, VLOOKUP(H13, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H13, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H13, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J13" s="58"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-    </row>
-    <row r="14" spans="2:17" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13" t="str">
+      <c r="J13" s="54"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+    </row>
+    <row r="14" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E14" s="13"/>
-      <c r="G14" s="13" t="str">
+      <c r="E14" s="10"/>
+      <c r="G14" s="10" t="str">
         <f>IF(F14=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F14,Sites!$A:$B,3,FALSE),VLOOKUP(F14,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H14" s="58"/>
-      <c r="I14" s="13" t="str">
+      <c r="H14" s="54"/>
+      <c r="I14" s="10" t="str">
         <f>IF(H14="", "", IF(E$3&lt;=7, VLOOKUP(H14, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H14, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H14, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J14" s="58"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-    </row>
-    <row r="15" spans="2:17" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13" t="str">
+      <c r="J14" s="54"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+    </row>
+    <row r="15" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="13" t="str">
+      <c r="E15" s="10"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="10" t="str">
         <f>IF(F15=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F15,Sites!$A:$B,3,FALSE),VLOOKUP(F15,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H15" s="58"/>
-      <c r="I15" s="13" t="str">
+      <c r="H15" s="54"/>
+      <c r="I15" s="10" t="str">
         <f>IF(H15="", "", IF(E$3&lt;=7, VLOOKUP(H15, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H15, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H15, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J15" s="58"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="58"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-    </row>
-    <row r="16" spans="2:17" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13" t="str">
+      <c r="J15" s="54"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="54"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+    </row>
+    <row r="16" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="13" t="str">
+      <c r="E16" s="10"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="10" t="str">
         <f>IF(F16=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F16,Sites!$A:$B,3,FALSE),VLOOKUP(F16,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H16" s="58"/>
-      <c r="I16" s="13" t="str">
+      <c r="H16" s="54"/>
+      <c r="I16" s="10" t="str">
         <f>IF(H16="", "", IF(E$3&lt;=7, VLOOKUP(H16, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H16, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H16, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J16" s="58"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-    </row>
-    <row r="17" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="13" t="str">
+      <c r="J16" s="54"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+    </row>
+    <row r="17" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="10" t="str">
         <f>IF(F17=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F17,Sites!$A:$B,3,FALSE),VLOOKUP(F17,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I17" s="13" t="str">
+      <c r="I17" s="10" t="str">
         <f>IF(H17="", "", IF(E$3&lt;=7, VLOOKUP(H17, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H17, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H17, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J17" s="58"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-    </row>
-    <row r="18" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="13" t="str">
+      <c r="J17" s="54"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+    </row>
+    <row r="18" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="10" t="str">
         <f>IF(F18=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F18,Sites!$A:$B,3,FALSE),VLOOKUP(F18,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H18" s="58"/>
-      <c r="I18" s="13" t="str">
+      <c r="H18" s="54"/>
+      <c r="I18" s="10" t="str">
         <f>IF(H18="", "", IF(E$3&lt;=7, VLOOKUP(H18, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H18, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H18, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J18" s="58"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-    </row>
-    <row r="19" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="G19" s="13" t="str">
+      <c r="J18" s="54"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+    </row>
+    <row r="19" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="G19" s="10" t="str">
         <f>IF(F19=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F19,Sites!$A:$B,3,FALSE),VLOOKUP(F19,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H19" s="58"/>
-      <c r="I19" s="13" t="str">
+      <c r="H19" s="54"/>
+      <c r="I19" s="10" t="str">
         <f>IF(H19="", "", IF(E$3&lt;=7, VLOOKUP(H19, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H19, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H19, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J19" s="58"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-    </row>
-    <row r="20" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B20" s="56"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="13" t="str">
+      <c r="J19" s="54"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+    </row>
+    <row r="20" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B20" s="52"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="10" t="str">
         <f>IF(F20=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F20,Sites!$A:$B,3,FALSE),VLOOKUP(F20,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H20" s="58"/>
-      <c r="I20" s="13" t="str">
+      <c r="H20" s="54"/>
+      <c r="I20" s="10" t="str">
         <f>IF(H20="", "", IF(E$3&lt;=7, VLOOKUP(H20, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H20, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H20, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J20" s="58"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="59"/>
-    </row>
-    <row r="21" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="13" t="str">
+      <c r="J20" s="54"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="55"/>
+    </row>
+    <row r="21" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="10" t="str">
         <f>IF(F21=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F21,Sites!$A:$B,3,FALSE),VLOOKUP(F21,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I21" s="13" t="str">
+      <c r="I21" s="10" t="str">
         <f>IF(H21="", "", IF(E$3&lt;=7, VLOOKUP(H21, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H21, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H21, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J21" s="58"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-    </row>
-    <row r="22" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="G22" s="13" t="str">
+      <c r="J21" s="54"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+    </row>
+    <row r="22" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="G22" s="10" t="str">
         <f>IF(F22=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F22,Sites!$A:$B,3,FALSE),VLOOKUP(F22,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H22" s="58"/>
-      <c r="I22" s="13" t="str">
+      <c r="H22" s="54"/>
+      <c r="I22" s="10" t="str">
         <f>IF(H22="", "", IF(E$3&lt;=7, VLOOKUP(H22, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H22, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H22, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J22" s="58"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-    </row>
-    <row r="23" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B23" s="12"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="G23" s="13" t="str">
+      <c r="J22" s="54"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+    </row>
+    <row r="23" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="G23" s="10" t="str">
         <f>IF(F23=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F23,Sites!$A:$B,3,FALSE),VLOOKUP(F23,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H23" s="58"/>
-      <c r="I23" s="13" t="str">
+      <c r="H23" s="54"/>
+      <c r="I23" s="10" t="str">
         <f>IF(H23="", "", IF(E$3&lt;=7, VLOOKUP(H23, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H23, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H23, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J23" s="58"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-    </row>
-    <row r="24" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="G24" s="13" t="str">
+      <c r="J23" s="54"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+    </row>
+    <row r="24" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="G24" s="10" t="str">
         <f>IF(F24=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F24,Sites!$A:$B,3,FALSE),VLOOKUP(F24,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H24" s="58"/>
-      <c r="I24" s="13" t="str">
+      <c r="H24" s="54"/>
+      <c r="I24" s="10" t="str">
         <f>IF(H24="", "", IF(E$3&lt;=7, VLOOKUP(H24, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H24, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H24, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J24" s="58"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-    </row>
-    <row r="25" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="G25" s="13" t="str">
+      <c r="J24" s="54"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+    </row>
+    <row r="25" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="G25" s="10" t="str">
         <f>IF(F25=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F25,Sites!$A:$B,3,FALSE),VLOOKUP(F25,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I25" s="13" t="str">
+      <c r="I25" s="10" t="str">
         <f>IF(H25="", "", IF(E$3&lt;=7, VLOOKUP(H25, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H25, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H25, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J25" s="58"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-    </row>
-    <row r="26" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="G26" s="13" t="str">
+      <c r="J25" s="54"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+    </row>
+    <row r="26" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="G26" s="10" t="str">
         <f>IF(F26=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F26,Sites!$A:$B,3,FALSE),VLOOKUP(F26,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I26" s="13" t="str">
+      <c r="I26" s="10" t="str">
         <f>IF(H26="", "", IF(E$3&lt;=7, VLOOKUP(H26, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H26, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H26, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J26" s="58"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="59"/>
-    </row>
-    <row r="27" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="G27" s="13" t="str">
+      <c r="J26" s="54"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="55"/>
+    </row>
+    <row r="27" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="G27" s="10" t="str">
         <f>IF(F27=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F27,Sites!$A:$B,3,FALSE),VLOOKUP(F27,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I27" s="13" t="str">
+      <c r="I27" s="10" t="str">
         <f>IF(H27="", "", IF(E$3&lt;=7, VLOOKUP(H27, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H27, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H27, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J27" s="58"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="59"/>
-    </row>
-    <row r="28" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="G28" s="13" t="str">
+      <c r="J27" s="54"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="55"/>
+    </row>
+    <row r="28" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="G28" s="10" t="str">
         <f>IF(F28=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F28,Sites!$A:$B,3,FALSE),VLOOKUP(F28,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I28" s="13" t="str">
+      <c r="I28" s="10" t="str">
         <f>IF(H28="", "", IF(E$3&lt;=7, VLOOKUP(H28, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H28, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H28, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J28" s="58"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="59"/>
-    </row>
-    <row r="29" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="G29" s="13" t="str">
+      <c r="J28" s="54"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="55"/>
+    </row>
+    <row r="29" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="G29" s="10" t="str">
         <f>IF(F29=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F29,Sites!$A:$B,3,FALSE),VLOOKUP(F29,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I29" s="13" t="str">
+      <c r="I29" s="10" t="str">
         <f>IF(H29="", "", IF(E$3&lt;=7, VLOOKUP(H29, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H29, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H29, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J29" s="58"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="59"/>
-    </row>
-    <row r="30" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="G30" s="13" t="str">
+      <c r="J29" s="54"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="55"/>
+    </row>
+    <row r="30" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="G30" s="10" t="str">
         <f>IF(F30=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F30,Sites!$A:$B,3,FALSE),VLOOKUP(F30,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I30" s="13" t="str">
+      <c r="I30" s="10" t="str">
         <f>IF(H30="", "", IF(E$3&lt;=7, VLOOKUP(H30, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H30, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H30, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J30" s="58"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="59"/>
-    </row>
-    <row r="31" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="G31" s="13" t="str">
+      <c r="J30" s="54"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="55"/>
+    </row>
+    <row r="31" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="G31" s="10" t="str">
         <f>IF(F31=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F31,Sites!$A:$B,3,FALSE),VLOOKUP(F31,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I31" s="13" t="str">
+      <c r="I31" s="10" t="str">
         <f>IF(H31="", "", IF(E$3&lt;=7, VLOOKUP(H31, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H31, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H31, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J31" s="58"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="59"/>
-    </row>
-    <row r="32" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="G32" s="13" t="str">
+      <c r="J31" s="54"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="55"/>
+    </row>
+    <row r="32" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="G32" s="10" t="str">
         <f>IF(F32=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F32,Sites!$A:$B,3,FALSE),VLOOKUP(F32,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I32" s="13" t="str">
+      <c r="I32" s="10" t="str">
         <f>IF(H32="", "", IF(E$3&lt;=7, VLOOKUP(H32, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H32, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H32, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J32" s="58"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="59"/>
-    </row>
-    <row r="33" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B33" s="12"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="G33" s="13" t="str">
+      <c r="J32" s="54"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="55"/>
+    </row>
+    <row r="33" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="G33" s="10" t="str">
         <f>IF(F33=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F33,Sites!$A:$B,3,FALSE),VLOOKUP(F33,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I33" s="13" t="str">
+      <c r="I33" s="10" t="str">
         <f>IF(H33="", "", IF(E$3&lt;=7, VLOOKUP(H33, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H33, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H33, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J33" s="58"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="59"/>
-    </row>
-    <row r="34" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B34" s="12"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="G34" s="13" t="str">
+      <c r="J33" s="54"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="55"/>
+    </row>
+    <row r="34" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="G34" s="10" t="str">
         <f>IF(F34=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F34,Sites!$A:$B,3,FALSE),VLOOKUP(F34,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I34" s="13" t="str">
+      <c r="I34" s="10" t="str">
         <f>IF(H34="", "", IF(E$3&lt;=7, VLOOKUP(H34, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H34, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H34, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J34" s="58"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="59"/>
-    </row>
-    <row r="35" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B35" s="12"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="13" t="str">
+      <c r="J34" s="54"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="55"/>
+    </row>
+    <row r="35" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="10" t="str">
         <f>IF(F35=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F35,Sites!$A:$B,3,FALSE),VLOOKUP(F35,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I35" s="13" t="str">
+      <c r="I35" s="10" t="str">
         <f>IF(H35="", "", IF(E$3&lt;=7, VLOOKUP(H35, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H35, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H35, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J35" s="58"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="59"/>
-    </row>
-    <row r="36" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="13" t="str">
+      <c r="J35" s="54"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="55"/>
+    </row>
+    <row r="36" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="10" t="str">
         <f>IF(F36=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F36,Sites!$A:$B,3,FALSE),VLOOKUP(F36,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I36" s="13" t="str">
+      <c r="I36" s="10" t="str">
         <f>IF(H36="", "", IF(E$3&lt;=7, VLOOKUP(H36, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H36, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H36, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J36" s="58"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="58"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="59"/>
-    </row>
-    <row r="37" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B37" s="12"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="13" t="str">
+      <c r="J36" s="54"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="55"/>
+    </row>
+    <row r="37" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="10" t="str">
         <f>IF(F37=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F37,Sites!$A:$B,3,FALSE),VLOOKUP(F37,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I37" s="13" t="str">
+      <c r="I37" s="10" t="str">
         <f>IF(H37="", "", IF(E$3&lt;=7, VLOOKUP(H37, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H37, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H37, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J37" s="58"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="58"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="59"/>
-    </row>
-    <row r="38" spans="2:16" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B38" s="12"/>
-      <c r="C38" s="60"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="13" t="str">
+      <c r="J37" s="54"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="12"/>
+      <c r="P37" s="55"/>
+    </row>
+    <row r="38" spans="2:16" s="8" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B38" s="9"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="10" t="str">
         <f>IF(F38=""," ",IF(J$2&gt;=DATE(2024,11,1),VLOOKUP(F38,Sites!$A:$B,3,FALSE),VLOOKUP(F38,Sites!$A:$A,2,FALSE)))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I38" s="13" t="str">
+      <c r="I38" s="10" t="str">
         <f>IF(H38="", "", IF(E$3&lt;=7, VLOOKUP(H38, Transfers!$A:$D, 2, FALSE),
                    IF(E$3&lt;=15, VLOOKUP(H38, Transfers!$A:$D, 3, FALSE),
                       VLOOKUP(H38, Transfers!$A:$D, 4, FALSE))))</f>
         <v/>
       </c>
-      <c r="J38" s="58"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B39" s="51"/>
-      <c r="C39" s="62">
+      <c r="J38" s="54"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="12"/>
+      <c r="P38" s="12"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="47"/>
+      <c r="C39" s="58">
         <f>IF((COUNTA(B10:B36)=0),0,SUM(C10:C38))</f>
         <v>0</v>
       </c>
-      <c r="D39" s="61">
+      <c r="D39" s="57">
         <f>IF((D10)=0,"  ",SUM(D10:D38))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="61" t="str">
+      <c r="E39" s="57" t="str">
         <f>IF((E10)=0,"  ",SUM(E10:E38))</f>
         <v xml:space="preserve">  </v>
       </c>
-      <c r="F39" s="62"/>
-      <c r="G39" s="64">
+      <c r="F39" s="58"/>
+      <c r="G39" s="60">
         <f>IF((G10)=0,"  ",SUM(G10:G38)/(M2))</f>
         <v>0</v>
       </c>
-      <c r="H39" s="53"/>
-      <c r="I39" s="54">
+      <c r="H39" s="49"/>
+      <c r="I39" s="50">
         <f>IF((G10)=" ",0,SUM(I10:I38)/$M$2/$E$3)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="53"/>
-      <c r="K39" s="52">
+      <c r="J39" s="49"/>
+      <c r="K39" s="48">
         <f>IF((K10)=0,0,SUM(K10:K38)/(M2))</f>
         <v>0</v>
       </c>
-      <c r="L39" s="53"/>
-      <c r="M39" s="54">
+      <c r="L39" s="49"/>
+      <c r="M39" s="50">
         <f>IF((L10)=0,"  ",SUM(M10:M38)/$M$2/$E$3)</f>
         <v>117.40041928721173</v>
       </c>
-      <c r="N39" s="54">
+      <c r="N39" s="50">
         <f>IF((M10)=" ","  ",SUM(N10:N38)/$E$3)</f>
         <v>0</v>
       </c>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-    </row>
-    <row r="41" spans="2:16" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="103" t="s">
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+    </row>
+    <row r="41" spans="2:16" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B41" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="104"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="34" t="s">
+      <c r="C41" s="99"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="22"/>
-    </row>
-    <row r="42" spans="2:16" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="100" t="s">
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="19"/>
+    </row>
+    <row r="42" spans="2:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="101"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="65" t="s">
+      <c r="C42" s="84"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="F42" s="71">
+      <c r="F42" s="66">
         <f>C39+G39+I39+K39+M39+N39+M3</f>
         <v>117.40041928721173</v>
       </c>
-      <c r="H42" s="17" t="s">
+      <c r="H42" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I42" s="102"/>
-      <c r="J42" s="102"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="23"/>
-    </row>
-    <row r="43" spans="2:16" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="100" t="s">
+      <c r="I42" s="85"/>
+      <c r="J42" s="85"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="20"/>
+    </row>
+    <row r="43" spans="2:16" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="101"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="24" t="s">
+      <c r="C43" s="84"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="22">
         <f>D39</f>
         <v>0</v>
       </c>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="26"/>
-    </row>
-    <row r="44" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="92" t="s">
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="20"/>
+    </row>
+    <row r="44" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="93"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="24" t="s">
+      <c r="C44" s="76"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F44" s="19" t="str">
+      <c r="F44" s="16" t="str">
         <f>E39</f>
         <v xml:space="preserve">  </v>
       </c>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="7"/>
-    </row>
-    <row r="45" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="15"/>
+    </row>
+    <row r="45" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -9080,7 +9063,7 @@
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="E46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -9088,6 +9071,11 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="14">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B4:N5"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="L6:N6"/>
@@ -9097,11 +9085,6 @@
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B4:N5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.511811023622047" bottom="0.55118110236220497" header="0.23622047244094499" footer="0.27559055118110198"/>
